--- a/kadro/ok.xlsx
+++ b/kadro/ok.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kahra\Desktop\ALL\D\Downloads\New folder\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kahra\OneDrive\Documents\GitHub\ulkemyanimda.github.io\kadro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9DCD7F9-7FD1-43E5-A682-E9A71FDC2EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30083AEC-4E55-405D-8C13-753391FD4C72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="84" yWindow="0" windowWidth="22956" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="84" yWindow="768" windowWidth="22956" windowHeight="8724" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1843,239 +1843,239 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>23</v>
+        <v>44</v>
+      </c>
+      <c r="C2" t="s">
+        <v>418</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>351</v>
+        <v>46</v>
+      </c>
+      <c r="F2" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>238</v>
+        <v>144</v>
       </c>
       <c r="B3" t="s">
-        <v>239</v>
+        <v>145</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>240</v>
+        <v>142</v>
       </c>
       <c r="E3" t="s">
-        <v>241</v>
-      </c>
-      <c r="F3" t="s">
-        <v>352</v>
+        <v>146</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
+        <v>197</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>179</v>
+        <v>118</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>353</v>
+        <v>198</v>
+      </c>
+      <c r="F4" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>181</v>
+        <v>332</v>
       </c>
       <c r="B5" t="s">
-        <v>182</v>
+        <v>325</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>183</v>
+        <v>333</v>
       </c>
       <c r="E5" t="s">
-        <v>184</v>
-      </c>
-      <c r="F5" t="s">
-        <v>358</v>
+        <v>334</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>56</v>
+        <v>172</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>57</v>
+        <v>173</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>58</v>
+        <v>174</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>59</v>
+        <v>175</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>414</v>
+        <v>176</v>
+      </c>
+      <c r="F6" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>288</v>
+        <v>185</v>
       </c>
       <c r="B7" t="s">
-        <v>289</v>
+        <v>186</v>
       </c>
       <c r="C7" t="s">
-        <v>290</v>
+        <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
-        <v>291</v>
+        <v>187</v>
       </c>
       <c r="F7" t="s">
-        <v>359</v>
+        <v>408</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>313</v>
+        <v>139</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C8" t="s">
-        <v>58</v>
+        <v>140</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>141</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>315</v>
+        <v>142</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>354</v>
+        <v>143</v>
+      </c>
+      <c r="F8" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B9" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C9" t="s">
-        <v>10</v>
+        <v>418</v>
       </c>
       <c r="D9" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="E9" t="s">
-        <v>248</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>414</v>
+        <v>252</v>
+      </c>
+      <c r="F9" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>277</v>
+        <v>47</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="C10" t="s">
-        <v>58</v>
+        <v>48</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>275</v>
+        <v>50</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>279</v>
+        <v>51</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>356</v>
+        <v>414</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="B11" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="E11" t="s">
-        <v>283</v>
-      </c>
-      <c r="F11" t="s">
-        <v>357</v>
+        <v>298</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>329</v>
+        <v>292</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>330</v>
+        <v>293</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>424</v>
+        <v>36</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>232</v>
+        <v>142</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>355</v>
+        <v>294</v>
+      </c>
+      <c r="F12" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>168</v>
+        <v>135</v>
       </c>
       <c r="B13" t="s">
-        <v>169</v>
+        <v>136</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="D13" t="s">
-        <v>170</v>
+        <v>137</v>
       </c>
       <c r="E13" t="s">
-        <v>171</v>
+        <v>138</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>414</v>
@@ -2083,196 +2083,199 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>120</v>
+        <v>263</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>121</v>
+        <v>264</v>
       </c>
       <c r="C14" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>122</v>
+        <v>37</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>123</v>
+        <v>265</v>
       </c>
       <c r="F14" t="s">
-        <v>362</v>
+        <v>404</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>309</v>
+        <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>310</v>
+        <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>423</v>
+        <v>23</v>
       </c>
       <c r="D15" t="s">
-        <v>311</v>
+        <v>6</v>
       </c>
       <c r="E15" t="s">
-        <v>312</v>
-      </c>
-      <c r="F15" t="s">
-        <v>361</v>
+        <v>7</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>150</v>
+        <v>109</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>424</v>
+        <v>36</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>414</v>
+        <v>111</v>
+      </c>
+      <c r="F16" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="B17" t="s">
-        <v>91</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>424</v>
+        <v>79</v>
+      </c>
+      <c r="C17" t="s">
+        <v>23</v>
       </c>
       <c r="D17" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="E17" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="F17" t="s">
-        <v>360</v>
+        <v>405</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F18" t="s">
-        <v>365</v>
+        <v>402</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>348</v>
+        <v>260</v>
       </c>
       <c r="B19" t="s">
-        <v>349</v>
-      </c>
-      <c r="C19" t="s">
-        <v>23</v>
+        <v>261</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>424</v>
       </c>
       <c r="D19" t="s">
-        <v>232</v>
+        <v>15</v>
+      </c>
+      <c r="E19" t="s">
+        <v>262</v>
       </c>
       <c r="F19" t="s">
-        <v>364</v>
+        <v>401</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>224</v>
+        <v>273</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>225</v>
+        <v>274</v>
       </c>
       <c r="C20" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>226</v>
+        <v>275</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>414</v>
+        <v>276</v>
+      </c>
+      <c r="F20" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>52</v>
+        <v>159</v>
       </c>
       <c r="B21" t="s">
-        <v>53</v>
+        <v>160</v>
       </c>
       <c r="C21" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="D21" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
       <c r="E21" t="s">
-        <v>55</v>
-      </c>
-      <c r="F21" t="s">
-        <v>363</v>
+        <v>161</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>131</v>
+        <v>74</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>414</v>
+        <v>77</v>
+      </c>
+      <c r="F22" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>68</v>
+        <v>256</v>
       </c>
       <c r="B23" t="s">
-        <v>69</v>
+        <v>257</v>
       </c>
       <c r="C23" t="s">
-        <v>420</v>
+        <v>10</v>
       </c>
       <c r="D23" t="s">
-        <v>50</v>
+        <v>258</v>
       </c>
       <c r="E23" t="s">
-        <v>70</v>
+        <v>259</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>414</v>
@@ -2280,199 +2283,199 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>317</v>
+        <v>17</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>318</v>
+        <v>18</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>417</v>
+        <v>19</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>319</v>
+        <v>15</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>367</v>
+        <v>20</v>
+      </c>
+      <c r="F24" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>326</v>
+        <v>64</v>
       </c>
       <c r="B25" t="s">
-        <v>327</v>
+        <v>65</v>
       </c>
       <c r="C25" t="s">
-        <v>10</v>
+        <v>422</v>
       </c>
       <c r="D25" t="s">
-        <v>170</v>
+        <v>37</v>
       </c>
       <c r="E25" t="s">
-        <v>328</v>
-      </c>
-      <c r="F25" t="s">
-        <v>366</v>
+        <v>66</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>425</v>
+        <v>106</v>
+      </c>
+      <c r="C26" t="s">
+        <v>10</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="F26" t="s">
-        <v>411</v>
+        <v>396</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>112</v>
+        <v>147</v>
       </c>
       <c r="B27" t="s">
-        <v>113</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>424</v>
+        <v>148</v>
+      </c>
+      <c r="C27" t="s">
+        <v>23</v>
       </c>
       <c r="D27" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="E27" t="s">
-        <v>115</v>
+        <v>149</v>
       </c>
       <c r="F27" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>153</v>
+        <v>221</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>417</v>
+        <v>222</v>
+      </c>
+      <c r="C28" t="s">
+        <v>10</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>142</v>
+        <v>11</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>414</v>
+        <v>223</v>
+      </c>
+      <c r="F28" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>85</v>
+        <v>192</v>
       </c>
       <c r="B29" t="s">
-        <v>86</v>
+        <v>193</v>
       </c>
       <c r="C29" t="s">
-        <v>419</v>
+        <v>23</v>
       </c>
       <c r="D29" t="s">
-        <v>88</v>
+        <v>194</v>
       </c>
       <c r="E29" t="s">
-        <v>89</v>
+        <v>195</v>
       </c>
       <c r="F29" t="s">
-        <v>370</v>
+        <v>395</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>19</v>
+        <v>98</v>
+      </c>
+      <c r="C30" t="s">
+        <v>10</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="F30" t="s">
-        <v>372</v>
+        <v>390</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>101</v>
+        <v>26</v>
       </c>
       <c r="B31" t="s">
-        <v>102</v>
+        <v>27</v>
       </c>
       <c r="C31" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="D31" t="s">
-        <v>103</v>
+        <v>28</v>
       </c>
       <c r="E31" t="s">
-        <v>104</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>414</v>
+        <v>29</v>
+      </c>
+      <c r="F31" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>338</v>
+        <v>299</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>19</v>
+        <v>300</v>
+      </c>
+      <c r="C32" t="s">
+        <v>58</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>37</v>
+        <v>118</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>340</v>
+        <v>301</v>
       </c>
       <c r="F32" t="s">
-        <v>373</v>
+        <v>392</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>188</v>
+        <v>94</v>
       </c>
       <c r="B33" t="s">
-        <v>189</v>
+        <v>95</v>
       </c>
       <c r="C33" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="D33" t="s">
-        <v>190</v>
+        <v>37</v>
       </c>
       <c r="E33" t="s">
-        <v>191</v>
+        <v>96</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>414</v>
@@ -2480,619 +2483,619 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>61</v>
+        <v>162</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>62</v>
+        <v>163</v>
       </c>
       <c r="C34" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>63</v>
+        <v>164</v>
       </c>
       <c r="F34" t="s">
-        <v>368</v>
+        <v>393</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="B35" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="C35" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="D35" t="s">
-        <v>11</v>
+        <v>219</v>
       </c>
       <c r="E35" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="F35" t="s">
-        <v>375</v>
+        <v>391</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>39</v>
+        <v>156</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C36" t="s">
-        <v>23</v>
+        <v>157</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>424</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>414</v>
+        <v>158</v>
+      </c>
+      <c r="F36" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="C37" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="D37" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="E37" t="s">
-        <v>38</v>
-      </c>
-      <c r="F37" t="s">
-        <v>374</v>
+        <v>12</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>266</v>
+        <v>71</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>267</v>
+        <v>72</v>
       </c>
       <c r="C38" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>126</v>
+        <v>28</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="F38" t="s">
-        <v>371</v>
+        <v>73</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>302</v>
+        <v>321</v>
       </c>
       <c r="B39" t="s">
-        <v>303</v>
+        <v>322</v>
       </c>
       <c r="C39" t="s">
-        <v>19</v>
+        <v>418</v>
       </c>
       <c r="D39" t="s">
-        <v>304</v>
+        <v>323</v>
       </c>
       <c r="E39" t="s">
-        <v>305</v>
-      </c>
-      <c r="F39" t="s">
-        <v>377</v>
+        <v>324</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>341</v>
+        <v>242</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>342</v>
+        <v>243</v>
       </c>
       <c r="C40" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>343</v>
+        <v>45</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="F40" t="s">
-        <v>379</v>
+        <v>244</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>199</v>
+        <v>306</v>
       </c>
       <c r="B41" t="s">
-        <v>200</v>
+        <v>307</v>
       </c>
       <c r="C41" t="s">
         <v>36</v>
       </c>
       <c r="D41" t="s">
-        <v>201</v>
+        <v>50</v>
       </c>
       <c r="E41" t="s">
-        <v>202</v>
+        <v>308</v>
       </c>
       <c r="F41" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>228</v>
-      </c>
-      <c r="B42" t="s">
-        <v>67</v>
+      <c r="A42" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="C42" t="s">
-        <v>36</v>
-      </c>
-      <c r="D42" t="s">
-        <v>142</v>
-      </c>
-      <c r="E42" t="s">
-        <v>229</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>414</v>
+        <v>10</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F42" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>336</v>
+      <c r="A43" t="s">
+        <v>269</v>
+      </c>
+      <c r="B43" t="s">
+        <v>270</v>
       </c>
       <c r="C43" t="s">
         <v>19</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="D43" t="s">
+        <v>271</v>
+      </c>
+      <c r="E43" t="s">
+        <v>272</v>
+      </c>
+      <c r="F43" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C44" t="s">
+        <v>19</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="F43" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>124</v>
-      </c>
-      <c r="B44" t="s">
-        <v>125</v>
-      </c>
-      <c r="C44" t="s">
-        <v>10</v>
-      </c>
-      <c r="D44" t="s">
-        <v>126</v>
-      </c>
-      <c r="E44" t="s">
-        <v>127</v>
+      <c r="E44" s="2" t="s">
+        <v>287</v>
       </c>
       <c r="F44" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>255</v>
+      <c r="A45" t="s">
+        <v>128</v>
+      </c>
+      <c r="B45" t="s">
+        <v>129</v>
+      </c>
+      <c r="C45" t="s">
+        <v>36</v>
+      </c>
+      <c r="D45" t="s">
+        <v>50</v>
+      </c>
+      <c r="E45" t="s">
+        <v>130</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+      <c r="A46" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C46" t="s">
+        <v>10</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="F46" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>165</v>
+      </c>
+      <c r="B47" t="s">
+        <v>166</v>
+      </c>
+      <c r="C47" t="s">
+        <v>23</v>
+      </c>
+      <c r="D47" t="s">
+        <v>50</v>
+      </c>
+      <c r="E47" t="s">
+        <v>167</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C48" t="s">
+        <v>10</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="F48" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>230</v>
+      </c>
+      <c r="B49" t="s">
+        <v>231</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="D49" t="s">
+        <v>232</v>
+      </c>
+      <c r="E49" t="s">
+        <v>233</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C50" t="s">
+        <v>10</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F50" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
         <v>345</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B51" t="s">
         <v>346</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C51" t="s">
         <v>36</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D51" t="s">
         <v>28</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E51" t="s">
         <v>347</v>
       </c>
-      <c r="F46" t="s">
+      <c r="F51" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C47" t="s">
-        <v>10</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F47" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>230</v>
-      </c>
-      <c r="B48" t="s">
-        <v>231</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="D48" t="s">
-        <v>232</v>
-      </c>
-      <c r="E48" t="s">
-        <v>233</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="C49" t="s">
-        <v>10</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="F49" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>165</v>
-      </c>
-      <c r="B50" t="s">
-        <v>166</v>
-      </c>
-      <c r="C50" t="s">
-        <v>23</v>
-      </c>
-      <c r="D50" t="s">
-        <v>50</v>
-      </c>
-      <c r="E50" t="s">
-        <v>167</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="C51" t="s">
-        <v>10</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="F51" t="s">
-        <v>383</v>
-      </c>
-    </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>128</v>
-      </c>
-      <c r="B52" t="s">
-        <v>129</v>
-      </c>
-      <c r="C52" t="s">
-        <v>36</v>
-      </c>
-      <c r="D52" t="s">
-        <v>50</v>
-      </c>
-      <c r="E52" t="s">
-        <v>130</v>
+      <c r="A52" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>255</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>285</v>
+      <c r="A53" t="s">
+        <v>124</v>
+      </c>
+      <c r="B53" t="s">
+        <v>125</v>
       </c>
       <c r="C53" t="s">
-        <v>19</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>287</v>
+        <v>10</v>
+      </c>
+      <c r="D53" t="s">
+        <v>126</v>
+      </c>
+      <c r="E53" t="s">
+        <v>127</v>
       </c>
       <c r="F53" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>269</v>
-      </c>
-      <c r="B54" t="s">
-        <v>270</v>
+      <c r="A54" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>336</v>
       </c>
       <c r="C54" t="s">
         <v>19</v>
       </c>
-      <c r="D54" t="s">
-        <v>271</v>
-      </c>
-      <c r="E54" t="s">
-        <v>272</v>
+      <c r="D54" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="F54" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>83</v>
+      <c r="A55" t="s">
+        <v>228</v>
+      </c>
+      <c r="B55" t="s">
+        <v>67</v>
       </c>
       <c r="C55" t="s">
-        <v>10</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F55" t="s">
-        <v>388</v>
+        <v>36</v>
+      </c>
+      <c r="D55" t="s">
+        <v>142</v>
+      </c>
+      <c r="E55" t="s">
+        <v>229</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>306</v>
+        <v>199</v>
       </c>
       <c r="B56" t="s">
-        <v>307</v>
+        <v>200</v>
       </c>
       <c r="C56" t="s">
         <v>36</v>
       </c>
       <c r="D56" t="s">
-        <v>50</v>
+        <v>201</v>
       </c>
       <c r="E56" t="s">
-        <v>308</v>
+        <v>202</v>
       </c>
       <c r="F56" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>242</v>
+        <v>341</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>243</v>
+        <v>342</v>
       </c>
       <c r="C57" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>45</v>
+        <v>343</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>414</v>
+        <v>344</v>
+      </c>
+      <c r="F57" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>321</v>
+        <v>302</v>
       </c>
       <c r="B58" t="s">
-        <v>322</v>
+        <v>303</v>
       </c>
       <c r="C58" t="s">
-        <v>418</v>
+        <v>19</v>
       </c>
       <c r="D58" t="s">
-        <v>323</v>
+        <v>304</v>
       </c>
       <c r="E58" t="s">
-        <v>324</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>414</v>
+        <v>305</v>
+      </c>
+      <c r="F58" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>71</v>
+        <v>266</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>72</v>
+        <v>267</v>
       </c>
       <c r="C59" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>28</v>
+        <v>126</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>414</v>
+        <v>268</v>
+      </c>
+      <c r="F59" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="B60" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="C60" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="D60" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="E60" t="s">
-        <v>12</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>414</v>
+        <v>38</v>
+      </c>
+      <c r="F60" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>156</v>
+        <v>39</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>424</v>
+        <v>40</v>
+      </c>
+      <c r="C61" t="s">
+        <v>23</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="F61" t="s">
-        <v>389</v>
+        <v>42</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="B62" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="C62" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="D62" t="s">
-        <v>219</v>
+        <v>11</v>
       </c>
       <c r="E62" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="F62" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>162</v>
+        <v>61</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>163</v>
+        <v>62</v>
       </c>
       <c r="C63" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>164</v>
+        <v>63</v>
       </c>
       <c r="F63" t="s">
-        <v>393</v>
+        <v>368</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>94</v>
+        <v>188</v>
       </c>
       <c r="B64" t="s">
-        <v>95</v>
+        <v>189</v>
       </c>
       <c r="C64" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D64" t="s">
-        <v>37</v>
+        <v>190</v>
       </c>
       <c r="E64" t="s">
-        <v>96</v>
+        <v>191</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>414</v>
@@ -3100,199 +3103,199 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>299</v>
+        <v>338</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="C65" t="s">
-        <v>58</v>
+        <v>339</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>118</v>
+        <v>37</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>301</v>
+        <v>340</v>
       </c>
       <c r="F65" t="s">
-        <v>392</v>
+        <v>373</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="B66" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="C66" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D66" t="s">
-        <v>28</v>
+        <v>103</v>
       </c>
       <c r="E66" t="s">
-        <v>29</v>
-      </c>
-      <c r="F66" t="s">
-        <v>394</v>
+        <v>104</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>97</v>
+        <v>30</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C67" t="s">
-        <v>10</v>
+        <v>31</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>99</v>
+        <v>32</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="F67" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>192</v>
+        <v>85</v>
       </c>
       <c r="B68" t="s">
-        <v>193</v>
+        <v>86</v>
       </c>
       <c r="C68" t="s">
-        <v>23</v>
+        <v>419</v>
       </c>
       <c r="D68" t="s">
-        <v>194</v>
+        <v>88</v>
       </c>
       <c r="E68" t="s">
-        <v>195</v>
+        <v>89</v>
       </c>
       <c r="F68" t="s">
-        <v>395</v>
+        <v>370</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>221</v>
+        <v>153</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="C69" t="s">
-        <v>10</v>
+        <v>154</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>417</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>11</v>
+        <v>142</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="F69" t="s">
-        <v>397</v>
+        <v>155</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="B70" t="s">
-        <v>148</v>
-      </c>
-      <c r="C70" t="s">
-        <v>23</v>
+        <v>113</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>424</v>
       </c>
       <c r="D70" t="s">
-        <v>54</v>
+        <v>114</v>
       </c>
       <c r="E70" t="s">
-        <v>149</v>
+        <v>115</v>
       </c>
       <c r="F70" t="s">
-        <v>398</v>
+        <v>369</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C71" t="s">
-        <v>10</v>
+        <v>117</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>425</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="F71" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>64</v>
+        <v>326</v>
       </c>
       <c r="B72" t="s">
-        <v>65</v>
+        <v>327</v>
       </c>
       <c r="C72" t="s">
-        <v>422</v>
+        <v>10</v>
       </c>
       <c r="D72" t="s">
-        <v>37</v>
+        <v>170</v>
       </c>
       <c r="E72" t="s">
-        <v>66</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>414</v>
+        <v>328</v>
+      </c>
+      <c r="F72" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>17</v>
+        <v>317</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>18</v>
+        <v>318</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>19</v>
+        <v>417</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>15</v>
+        <v>319</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F73" t="s">
-        <v>350</v>
+        <v>320</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>256</v>
+        <v>68</v>
       </c>
       <c r="B74" t="s">
-        <v>257</v>
+        <v>69</v>
       </c>
       <c r="C74" t="s">
-        <v>10</v>
+        <v>420</v>
       </c>
       <c r="D74" t="s">
-        <v>258</v>
+        <v>50</v>
       </c>
       <c r="E74" t="s">
-        <v>259</v>
+        <v>70</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>414</v>
@@ -3300,199 +3303,196 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F75" t="s">
-        <v>399</v>
+        <v>134</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>159</v>
+        <v>52</v>
       </c>
       <c r="B76" t="s">
-        <v>160</v>
+        <v>53</v>
       </c>
       <c r="C76" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="D76" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="E76" t="s">
-        <v>161</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>414</v>
+        <v>55</v>
+      </c>
+      <c r="F76" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>273</v>
+        <v>224</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>274</v>
+        <v>225</v>
       </c>
       <c r="C77" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>275</v>
+        <v>226</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="F77" t="s">
-        <v>400</v>
+        <v>227</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>260</v>
+        <v>348</v>
       </c>
       <c r="B78" t="s">
-        <v>261</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>424</v>
+        <v>349</v>
+      </c>
+      <c r="C78" t="s">
+        <v>23</v>
       </c>
       <c r="D78" t="s">
-        <v>15</v>
-      </c>
-      <c r="E78" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="F78" t="s">
-        <v>401</v>
+        <v>364</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C79" t="s">
         <v>10</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="F79" t="s">
-        <v>402</v>
+        <v>365</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="B80" t="s">
-        <v>79</v>
-      </c>
-      <c r="C80" t="s">
-        <v>23</v>
+        <v>91</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>424</v>
       </c>
       <c r="D80" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="E80" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="F80" t="s">
-        <v>405</v>
+        <v>360</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>110</v>
+        <v>151</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>36</v>
+        <v>424</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F81" t="s">
-        <v>406</v>
+        <v>152</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>4</v>
+        <v>309</v>
       </c>
       <c r="B82" t="s">
-        <v>5</v>
+        <v>310</v>
       </c>
       <c r="C82" t="s">
-        <v>23</v>
+        <v>423</v>
       </c>
       <c r="D82" t="s">
-        <v>6</v>
+        <v>311</v>
       </c>
       <c r="E82" t="s">
-        <v>7</v>
-      </c>
-      <c r="F82" s="2" t="s">
-        <v>414</v>
+        <v>312</v>
+      </c>
+      <c r="F82" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>263</v>
+        <v>120</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>264</v>
+        <v>121</v>
       </c>
       <c r="C83" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>37</v>
+        <v>122</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>265</v>
+        <v>123</v>
       </c>
       <c r="F83" t="s">
-        <v>404</v>
+        <v>362</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>135</v>
+        <v>168</v>
       </c>
       <c r="B84" t="s">
-        <v>136</v>
+        <v>169</v>
       </c>
       <c r="C84" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D84" t="s">
-        <v>137</v>
+        <v>170</v>
       </c>
       <c r="E84" t="s">
-        <v>138</v>
+        <v>171</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>414</v>
@@ -3500,227 +3500,227 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>292</v>
+        <v>329</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>293</v>
+        <v>330</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>36</v>
+        <v>424</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>142</v>
+        <v>232</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="F85" t="s">
-        <v>403</v>
+        <v>331</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="B86" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="C86" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="D86" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="E86" t="s">
-        <v>298</v>
-      </c>
-      <c r="F86" s="2" t="s">
-        <v>414</v>
+        <v>283</v>
+      </c>
+      <c r="F86" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>47</v>
+        <v>277</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>49</v>
+        <v>278</v>
+      </c>
+      <c r="C87" t="s">
+        <v>58</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>50</v>
+        <v>275</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>51</v>
+        <v>279</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>414</v>
+        <v>356</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B88" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C88" t="s">
-        <v>418</v>
+        <v>10</v>
       </c>
       <c r="D88" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="E88" t="s">
-        <v>252</v>
-      </c>
-      <c r="F88" t="s">
-        <v>409</v>
+        <v>248</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>139</v>
+        <v>313</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>141</v>
+        <v>314</v>
+      </c>
+      <c r="C89" t="s">
+        <v>58</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>142</v>
+        <v>315</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="F89" t="s">
-        <v>407</v>
+        <v>316</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>185</v>
+        <v>288</v>
       </c>
       <c r="B90" t="s">
-        <v>186</v>
+        <v>289</v>
       </c>
       <c r="C90" t="s">
-        <v>10</v>
+        <v>290</v>
       </c>
       <c r="D90" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="E90" t="s">
-        <v>187</v>
+        <v>291</v>
       </c>
       <c r="F90" t="s">
-        <v>408</v>
+        <v>359</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
-        <v>172</v>
+        <v>56</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>173</v>
+        <v>57</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>174</v>
+        <v>58</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>175</v>
+        <v>59</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F91" t="s">
-        <v>413</v>
+        <v>60</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>332</v>
+        <v>181</v>
       </c>
       <c r="B92" t="s">
-        <v>325</v>
+        <v>182</v>
       </c>
       <c r="C92" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D92" t="s">
-        <v>333</v>
+        <v>183</v>
       </c>
       <c r="E92" t="s">
-        <v>334</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>414</v>
+        <v>184</v>
+      </c>
+      <c r="F92" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>36</v>
+        <v>178</v>
+      </c>
+      <c r="C93" t="s">
+        <v>19</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>118</v>
+        <v>179</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="F93" t="s">
-        <v>410</v>
+        <v>180</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>144</v>
+        <v>238</v>
       </c>
       <c r="B94" t="s">
-        <v>145</v>
+        <v>239</v>
       </c>
       <c r="C94" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="D94" t="s">
-        <v>142</v>
+        <v>240</v>
       </c>
       <c r="E94" t="s">
-        <v>146</v>
-      </c>
-      <c r="F94" s="2" t="s">
-        <v>414</v>
+        <v>241</v>
+      </c>
+      <c r="F94" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C95" t="s">
-        <v>418</v>
+        <v>22</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F95" t="s">
-        <v>412</v>
+        <v>25</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>351</v>
       </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F95">
-    <sortCondition ref="B1:B95"/>
+    <sortCondition descending="1" ref="B1:B95"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/kadro/ok.xlsx
+++ b/kadro/ok.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kahra\OneDrive\Documents\GitHub\ulkemyanimda.github.io\kadro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{704D42B9-8678-4767-A7CD-4925831D30CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0919C4C-9358-4258-8990-3DB3BC7173CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1272,7 +1272,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1284,17 +1284,20 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1604,7 +1607,7 @@
     <col min="2" max="2" width="23.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="255.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.109375" customWidth="1"/>
     <col min="6" max="6" width="20.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1629,1400 +1632,1400 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>326</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="A2" s="9"/>
+      <c r="B2" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3"/>
+      <c r="B3" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" t="s">
+        <v>309</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3"/>
+      <c r="B4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F4" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3"/>
+      <c r="B5" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F5" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3"/>
+      <c r="B6" t="s">
+        <v>173</v>
+      </c>
+      <c r="C6" t="s">
+        <v>309</v>
+      </c>
+      <c r="D6" t="s">
+        <v>174</v>
+      </c>
+      <c r="E6" t="s">
+        <v>175</v>
+      </c>
+      <c r="F6" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3"/>
+      <c r="B7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C7" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
-        <v>166</v>
-      </c>
-      <c r="E2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F2" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>190</v>
-      </c>
-      <c r="F3" s="2"/>
-    </row>
-    <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="C4" t="s">
-        <v>328</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="D7" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>319</v>
-      </c>
-      <c r="C5" t="s">
-        <v>329</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="E7" t="s">
+        <v>128</v>
+      </c>
+      <c r="F7" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="7"/>
+      <c r="B8" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F8" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3"/>
+      <c r="B9" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>320</v>
-      </c>
-      <c r="C6" t="s">
-        <v>330</v>
-      </c>
-      <c r="D6" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="C7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>323</v>
-      </c>
-      <c r="C8" t="s">
-        <v>331</v>
-      </c>
-      <c r="D8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="2"/>
-    </row>
-    <row r="9" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>324</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="E9" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F9" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3"/>
+      <c r="B10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" t="s">
         <v>16</v>
       </c>
-      <c r="D9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="C10" t="s">
-        <v>40</v>
-      </c>
       <c r="D10" t="s">
-        <v>332</v>
+        <v>54</v>
+      </c>
+      <c r="E10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3"/>
-      <c r="B11" s="8" t="s">
-        <v>121</v>
+      <c r="B11" s="2" t="s">
+        <v>183</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>122</v>
+        <v>25</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>245</v>
+        <v>184</v>
+      </c>
+      <c r="F11" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3"/>
-      <c r="B12" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="C12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" t="s">
-        <v>125</v>
-      </c>
-      <c r="E12" t="s">
-        <v>126</v>
+      <c r="B12" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>203</v>
       </c>
       <c r="F12" t="s">
-        <v>250</v>
+        <v>294</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3"/>
       <c r="B13" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>40</v>
+        <v>147</v>
+      </c>
+      <c r="C13" t="s">
+        <v>7</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>41</v>
+        <v>148</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>305</v>
+        <v>149</v>
+      </c>
+      <c r="F13" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3"/>
       <c r="B14" t="s">
-        <v>199</v>
-      </c>
-      <c r="C14" t="s">
-        <v>200</v>
+        <v>181</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>314</v>
       </c>
       <c r="D14" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="E14" t="s">
-        <v>201</v>
+        <v>182</v>
       </c>
       <c r="F14" t="s">
-        <v>251</v>
+        <v>292</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3"/>
       <c r="B15" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="C15" t="s">
-        <v>40</v>
+        <v>50</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>312</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>218</v>
+        <v>51</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>246</v>
+        <v>52</v>
+      </c>
+      <c r="F15" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3"/>
-      <c r="B16" s="7" t="s">
-        <v>170</v>
+      <c r="B16" t="s">
+        <v>100</v>
       </c>
       <c r="C16" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D16" t="s">
-        <v>171</v>
+        <v>37</v>
       </c>
       <c r="E16" t="s">
-        <v>172</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>305</v>
+        <v>101</v>
+      </c>
+      <c r="F16" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3"/>
-      <c r="B17" s="10" t="s">
-        <v>191</v>
+      <c r="B17" s="2" t="s">
+        <v>153</v>
       </c>
       <c r="C17" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>190</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>248</v>
+        <v>154</v>
+      </c>
+      <c r="F17" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3"/>
-      <c r="B18" t="s">
-        <v>193</v>
+      <c r="B18" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="C18" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18" t="s">
-        <v>194</v>
-      </c>
-      <c r="E18" t="s">
-        <v>195</v>
+        <v>7</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="F18" t="s">
-        <v>249</v>
+        <v>288</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3"/>
-      <c r="B19" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>247</v>
+      <c r="B19" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="C19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" t="s">
+        <v>133</v>
+      </c>
+      <c r="E19" t="s">
+        <v>134</v>
+      </c>
+      <c r="F19" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3"/>
       <c r="B20" t="s">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D20" t="s">
-        <v>115</v>
+        <v>18</v>
       </c>
       <c r="E20" t="s">
-        <v>116</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>305</v>
+        <v>19</v>
+      </c>
+      <c r="F20" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3"/>
       <c r="B21" s="2" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="C21" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>83</v>
+        <v>25</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="F21" t="s">
-        <v>254</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3"/>
-      <c r="B22" t="s">
-        <v>214</v>
+      <c r="B22" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="C22" t="s">
-        <v>313</v>
-      </c>
-      <c r="D22" t="s">
-        <v>215</v>
-      </c>
-      <c r="E22" t="s">
-        <v>216</v>
+        <v>40</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>208</v>
       </c>
       <c r="F22" t="s">
-        <v>253</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3"/>
-      <c r="B23" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>305</v>
+      <c r="B23" t="s">
+        <v>150</v>
+      </c>
+      <c r="C23" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" t="s">
+        <v>151</v>
+      </c>
+      <c r="E23" t="s">
+        <v>152</v>
+      </c>
+      <c r="F23" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3"/>
-      <c r="B24" t="s">
-        <v>61</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="D24" t="s">
-        <v>62</v>
-      </c>
-      <c r="E24" t="s">
-        <v>63</v>
+      <c r="B24" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="F24" t="s">
-        <v>252</v>
+        <v>282</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3"/>
       <c r="B25" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C25" t="s">
-        <v>7</v>
+        <v>106</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>314</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>145</v>
+        <v>25</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="F25" t="s">
-        <v>257</v>
+        <v>281</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3"/>
-      <c r="B26" t="s">
-        <v>242</v>
+      <c r="B26" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="C26" t="s">
-        <v>16</v>
-      </c>
-      <c r="D26" t="s">
-        <v>160</v>
+        <v>7</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="F26" t="s">
-        <v>256</v>
+        <v>280</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3"/>
-      <c r="B27" s="2" t="s">
-        <v>155</v>
+      <c r="B27" t="s">
+        <v>212</v>
       </c>
       <c r="C27" t="s">
-        <v>7</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>305</v>
+        <v>24</v>
+      </c>
+      <c r="D27" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27" t="s">
+        <v>213</v>
+      </c>
+      <c r="F27" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3"/>
-      <c r="B28" t="s">
-        <v>333</v>
+      <c r="B28" s="2" t="s">
+        <v>140</v>
       </c>
       <c r="C28" t="s">
         <v>7</v>
       </c>
-      <c r="D28" t="s">
-        <v>37</v>
-      </c>
-      <c r="E28" t="s">
-        <v>38</v>
+      <c r="D28" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>141</v>
       </c>
       <c r="F28" t="s">
-        <v>255</v>
+        <v>278</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3"/>
-      <c r="B29" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>305</v>
+      <c r="B29" t="s">
+        <v>187</v>
+      </c>
+      <c r="C29" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" t="s">
+        <v>188</v>
+      </c>
+      <c r="E29" t="s">
+        <v>189</v>
+      </c>
+      <c r="F29" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="3"/>
-      <c r="B30" t="s">
-        <v>46</v>
+      <c r="B30" s="2" t="s">
+        <v>196</v>
       </c>
       <c r="C30" t="s">
-        <v>311</v>
-      </c>
-      <c r="D30" t="s">
-        <v>35</v>
-      </c>
-      <c r="E30" t="s">
-        <v>47</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>305</v>
+        <v>14</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="F30" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3"/>
       <c r="B31" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>308</v>
+        <v>162</v>
+      </c>
+      <c r="C31" t="s">
+        <v>7</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>221</v>
+        <v>163</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>259</v>
+        <v>164</v>
+      </c>
+      <c r="F31" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3"/>
       <c r="B32" t="s">
-        <v>227</v>
+        <v>85</v>
       </c>
       <c r="C32" t="s">
         <v>7</v>
       </c>
       <c r="D32" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="E32" t="s">
-        <v>228</v>
+        <v>87</v>
       </c>
       <c r="F32" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="3"/>
-      <c r="B33" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>81</v>
+      <c r="B33" t="s">
+        <v>240</v>
+      </c>
+      <c r="C33" t="s">
+        <v>24</v>
+      </c>
+      <c r="D33" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" t="s">
+        <v>241</v>
       </c>
       <c r="F33" t="s">
-        <v>302</v>
+        <v>273</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="3"/>
-      <c r="B34" t="s">
-        <v>316</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="D34" t="s">
-        <v>77</v>
-      </c>
-      <c r="E34" t="s">
-        <v>78</v>
+      <c r="B34" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="F34" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3"/>
       <c r="B35" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>308</v>
+        <v>237</v>
+      </c>
+      <c r="C35" t="s">
+        <v>7</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>98</v>
+        <v>238</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>305</v>
+        <v>239</v>
+      </c>
+      <c r="F35" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="3"/>
-      <c r="B36" t="s">
-        <v>58</v>
+      <c r="B36" s="2" t="s">
+        <v>233</v>
       </c>
       <c r="C36" t="s">
-        <v>310</v>
-      </c>
-      <c r="D36" t="s">
-        <v>59</v>
-      </c>
-      <c r="E36" t="s">
-        <v>60</v>
+        <v>14</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>234</v>
       </c>
       <c r="F36" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3"/>
-      <c r="B37" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C37" s="2" t="s">
+      <c r="B37" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C37" t="s">
         <v>14</v>
       </c>
-      <c r="D37" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>22</v>
+      <c r="D37" t="s">
+        <v>210</v>
+      </c>
+      <c r="E37" t="s">
+        <v>211</v>
       </c>
       <c r="F37" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="3"/>
       <c r="B38" t="s">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="C38" t="s">
         <v>24</v>
       </c>
       <c r="D38" t="s">
-        <v>70</v>
+        <v>138</v>
       </c>
       <c r="E38" t="s">
-        <v>71</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>305</v>
+        <v>139</v>
+      </c>
+      <c r="F38" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="3"/>
-      <c r="B39" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>236</v>
+      <c r="B39" t="s">
+        <v>142</v>
+      </c>
+      <c r="C39" t="s">
+        <v>40</v>
+      </c>
+      <c r="D39" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" t="s">
+        <v>143</v>
       </c>
       <c r="F39" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3"/>
       <c r="B40" t="s">
-        <v>129</v>
+        <v>23</v>
       </c>
       <c r="C40" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="D40" t="s">
-        <v>130</v>
+        <v>25</v>
       </c>
       <c r="E40" t="s">
-        <v>131</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>305</v>
+        <v>26</v>
+      </c>
+      <c r="F40" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="3"/>
       <c r="B41" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C41" t="s">
-        <v>7</v>
+        <v>235</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>44</v>
+        <v>236</v>
       </c>
       <c r="F41" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="3"/>
-      <c r="B42" t="s">
-        <v>142</v>
-      </c>
-      <c r="C42" t="s">
-        <v>40</v>
-      </c>
-      <c r="D42" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" t="s">
-        <v>143</v>
+      <c r="B42" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="F42" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="3"/>
       <c r="B43" s="2" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="C43" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>28</v>
+        <v>86</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>305</v>
+        <v>186</v>
+      </c>
+      <c r="F43" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="3"/>
       <c r="B44" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="C44" t="s">
-        <v>24</v>
+        <v>310</v>
       </c>
       <c r="D44" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="E44" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="F44" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="3"/>
-      <c r="B45" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C45" t="s">
+      <c r="B45" t="s">
+        <v>316</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D45" t="s">
+        <v>77</v>
+      </c>
+      <c r="E45" t="s">
+        <v>78</v>
+      </c>
+      <c r="F45" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="9"/>
+      <c r="B46" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C46" t="s">
         <v>7</v>
       </c>
-      <c r="D45" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="F45" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="3"/>
-      <c r="B46" t="s">
-        <v>209</v>
-      </c>
-      <c r="C46" t="s">
-        <v>14</v>
-      </c>
-      <c r="D46" t="s">
-        <v>210</v>
-      </c>
-      <c r="E46" t="s">
-        <v>211</v>
+      <c r="D46" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F46" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="3"/>
-      <c r="B47" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="C47" t="s">
-        <v>7</v>
+      <c r="B47" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>308</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="F47" t="s">
-        <v>271</v>
+        <v>222</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="3"/>
       <c r="B48" t="s">
-        <v>137</v>
+        <v>227</v>
       </c>
       <c r="C48" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="D48" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="E48" t="s">
-        <v>139</v>
+        <v>228</v>
       </c>
       <c r="F48" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="3"/>
-      <c r="B49" t="s">
-        <v>45</v>
+      <c r="B49" s="10" t="s">
+        <v>144</v>
       </c>
       <c r="C49" t="s">
-        <v>24</v>
-      </c>
-      <c r="D49" t="s">
-        <v>98</v>
-      </c>
-      <c r="E49" t="s">
-        <v>158</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>305</v>
+        <v>7</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F49" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="3"/>
-      <c r="B50" s="2" t="s">
-        <v>233</v>
+      <c r="B50" t="s">
+        <v>242</v>
       </c>
       <c r="C50" t="s">
-        <v>14</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>234</v>
+        <v>16</v>
+      </c>
+      <c r="D50" t="s">
+        <v>160</v>
       </c>
       <c r="F50" t="s">
-        <v>270</v>
+        <v>256</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="3"/>
       <c r="B51" t="s">
-        <v>85</v>
+        <v>333</v>
       </c>
       <c r="C51" t="s">
         <v>7</v>
       </c>
       <c r="D51" t="s">
-        <v>86</v>
+        <v>37</v>
       </c>
       <c r="E51" t="s">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="F51" t="s">
-        <v>274</v>
+        <v>255</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="3"/>
-      <c r="B52" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>308</v>
+      <c r="B52" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C52" t="s">
+        <v>7</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>305</v>
+        <v>84</v>
+      </c>
+      <c r="F52" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="3"/>
-      <c r="B53" t="s">
-        <v>240</v>
+      <c r="B53" s="6" t="s">
+        <v>214</v>
       </c>
       <c r="C53" t="s">
-        <v>24</v>
+        <v>313</v>
       </c>
       <c r="D53" t="s">
-        <v>18</v>
+        <v>215</v>
       </c>
       <c r="E53" t="s">
-        <v>241</v>
+        <v>216</v>
       </c>
       <c r="F53" t="s">
-        <v>273</v>
+        <v>253</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="3"/>
-      <c r="B54" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C54" t="s">
-        <v>7</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>12</v>
+      <c r="B54" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D54" t="s">
+        <v>62</v>
+      </c>
+      <c r="E54" t="s">
+        <v>63</v>
       </c>
       <c r="F54" t="s">
-        <v>272</v>
+        <v>252</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="3"/>
-      <c r="B55" t="s">
-        <v>159</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>314</v>
+      <c r="B55" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="C55" t="s">
+        <v>200</v>
       </c>
       <c r="D55" t="s">
-        <v>160</v>
+        <v>35</v>
       </c>
       <c r="E55" t="s">
-        <v>161</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>305</v>
+        <v>201</v>
+      </c>
+      <c r="F55" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="3"/>
-      <c r="B56" s="2" t="s">
-        <v>140</v>
+      <c r="B56" t="s">
+        <v>124</v>
       </c>
       <c r="C56" t="s">
         <v>7</v>
       </c>
-      <c r="D56" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>141</v>
+      <c r="D56" t="s">
+        <v>125</v>
+      </c>
+      <c r="E56" t="s">
+        <v>126</v>
       </c>
       <c r="F56" t="s">
-        <v>278</v>
+        <v>250</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="3"/>
       <c r="B57" t="s">
-        <v>112</v>
+        <v>193</v>
       </c>
       <c r="C57" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D57" t="s">
-        <v>35</v>
+        <v>194</v>
       </c>
       <c r="E57" t="s">
-        <v>113</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>305</v>
+        <v>195</v>
+      </c>
+      <c r="F57" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="3"/>
-      <c r="B58" s="2" t="s">
-        <v>162</v>
+      <c r="B58" s="10" t="s">
+        <v>191</v>
       </c>
       <c r="C58" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F58" t="s">
-        <v>275</v>
+        <v>192</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="3"/>
-      <c r="B59" t="s">
-        <v>88</v>
-      </c>
-      <c r="C59" t="s">
-        <v>24</v>
-      </c>
-      <c r="D59" t="s">
-        <v>35</v>
-      </c>
-      <c r="E59" t="s">
-        <v>89</v>
+      <c r="B59" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>230</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>305</v>
+        <v>247</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="3"/>
       <c r="B60" s="2" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="C60" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="F60" t="s">
-        <v>276</v>
+        <v>219</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="3"/>
-      <c r="B61" t="s">
-        <v>187</v>
+      <c r="B61" s="10" t="s">
+        <v>121</v>
       </c>
       <c r="C61" t="s">
         <v>14</v>
       </c>
-      <c r="D61" t="s">
-        <v>188</v>
-      </c>
-      <c r="E61" t="s">
-        <v>189</v>
-      </c>
-      <c r="F61" t="s">
-        <v>277</v>
+      <c r="D61" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="3"/>
-      <c r="B62" s="2" t="s">
-        <v>56</v>
+      <c r="A62" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>165</v>
       </c>
       <c r="C62" t="s">
         <v>7</v>
       </c>
-      <c r="D62" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>57</v>
+      <c r="D62" t="s">
+        <v>166</v>
+      </c>
+      <c r="E62" t="s">
+        <v>167</v>
       </c>
       <c r="F62" t="s">
-        <v>280</v>
+        <v>244</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="3"/>
-      <c r="B63" t="s">
-        <v>212</v>
-      </c>
-      <c r="C63" t="s">
-        <v>24</v>
-      </c>
-      <c r="D63" t="s">
-        <v>35</v>
-      </c>
-      <c r="E63" t="s">
-        <v>213</v>
+      <c r="B63" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="F63" t="s">
-        <v>279</v>
+        <v>243</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="3"/>
-      <c r="B64" s="2" t="s">
-        <v>168</v>
+      <c r="A64" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>317</v>
       </c>
       <c r="C64" t="s">
+        <v>7</v>
+      </c>
+      <c r="D64" t="s">
+        <v>190</v>
+      </c>
+      <c r="F64" s="2"/>
+    </row>
+    <row r="65" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="C65" t="s">
+        <v>328</v>
+      </c>
+      <c r="D65" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="C66" t="s">
+        <v>329</v>
+      </c>
+      <c r="D66" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="C67" t="s">
+        <v>330</v>
+      </c>
+      <c r="D67" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B68" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="C68" t="s">
         <v>40</v>
       </c>
-      <c r="D64" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="3"/>
-      <c r="B65" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="C65" t="s">
-        <v>309</v>
-      </c>
-      <c r="D65" t="s">
-        <v>224</v>
-      </c>
-      <c r="E65" t="s">
-        <v>225</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="3"/>
-      <c r="B66" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C66" t="s">
+      <c r="D68" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E68" s="2"/>
+    </row>
+    <row r="69" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="C69" t="s">
+        <v>331</v>
+      </c>
+      <c r="D69" t="s">
+        <v>25</v>
+      </c>
+      <c r="F69" s="2"/>
+    </row>
+    <row r="70" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="C70" t="s">
+        <v>16</v>
+      </c>
+      <c r="D70" t="s">
+        <v>25</v>
+      </c>
+      <c r="F70" s="2"/>
+    </row>
+    <row r="71" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="B71" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="C71" t="s">
         <v>40</v>
       </c>
-      <c r="D66" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="3"/>
-      <c r="B67" t="s">
-        <v>6</v>
-      </c>
-      <c r="C67" t="s">
-        <v>7</v>
-      </c>
-      <c r="D67" t="s">
-        <v>8</v>
-      </c>
-      <c r="E67" t="s">
-        <v>9</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="3"/>
-      <c r="B68" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="F68" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="3"/>
-      <c r="B69" t="s">
-        <v>150</v>
-      </c>
-      <c r="C69" t="s">
-        <v>7</v>
-      </c>
-      <c r="D69" t="s">
-        <v>151</v>
-      </c>
-      <c r="E69" t="s">
-        <v>152</v>
-      </c>
-      <c r="F69" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="3"/>
-      <c r="B70" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C70" t="s">
-        <v>40</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F70" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="3"/>
-      <c r="B71" t="s">
-        <v>64</v>
-      </c>
-      <c r="C71" t="s">
-        <v>16</v>
-      </c>
       <c r="D71" t="s">
-        <v>25</v>
-      </c>
-      <c r="E71" t="s">
-        <v>65</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>305</v>
+        <v>332</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="3"/>
-      <c r="B72" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C72" t="s">
-        <v>40</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="F72" t="s">
-        <v>284</v>
-      </c>
+      <c r="A72" s="9"/>
+      <c r="B72" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="F72" s="2"/>
     </row>
     <row r="73" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="3"/>
-      <c r="B73" t="s">
-        <v>17</v>
-      </c>
-      <c r="C73" t="s">
-        <v>16</v>
-      </c>
-      <c r="D73" t="s">
-        <v>18</v>
-      </c>
-      <c r="E73" t="s">
-        <v>19</v>
-      </c>
-      <c r="F73" t="s">
-        <v>286</v>
+      <c r="B73" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="5"/>
-      <c r="B74" s="2" t="s">
-        <v>66</v>
+      <c r="A74" s="3"/>
+      <c r="B74" s="6" t="s">
+        <v>170</v>
       </c>
       <c r="C74" t="s">
         <v>7</v>
       </c>
-      <c r="D74" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F74" t="s">
-        <v>282</v>
+      <c r="D74" t="s">
+        <v>171</v>
+      </c>
+      <c r="E74" t="s">
+        <v>172</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="3"/>
-      <c r="B75" s="7" t="s">
-        <v>132</v>
+      <c r="B75" t="s">
+        <v>114</v>
       </c>
       <c r="C75" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D75" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="E75" t="s">
-        <v>134</v>
-      </c>
-      <c r="F75" t="s">
-        <v>287</v>
+        <v>116</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="3"/>
-      <c r="B76" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="C76" t="s">
-        <v>7</v>
+      <c r="B76" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>314</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="F76" t="s">
-        <v>289</v>
+        <v>103</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="3"/>
-      <c r="B77" t="s">
-        <v>100</v>
+      <c r="B77" s="7" t="s">
+        <v>155</v>
       </c>
       <c r="C77" t="s">
-        <v>16</v>
-      </c>
-      <c r="D77" t="s">
-        <v>37</v>
-      </c>
-      <c r="E77" t="s">
-        <v>101</v>
-      </c>
-      <c r="F77" t="s">
-        <v>290</v>
+        <v>7</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="3"/>
-      <c r="B78" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C78" t="s">
-        <v>7</v>
+      <c r="B78" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>314</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F78" t="s">
-        <v>288</v>
+        <v>92</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="3"/>
-      <c r="B79" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="F79" s="2"/>
+      <c r="B79" t="s">
+        <v>46</v>
+      </c>
+      <c r="C79" t="s">
+        <v>311</v>
+      </c>
+      <c r="D79" t="s">
+        <v>35</v>
+      </c>
+      <c r="E79" t="s">
+        <v>47</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="80" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="3"/>
-      <c r="B80" s="8" t="s">
-        <v>13</v>
+      <c r="B80" s="2" t="s">
+        <v>104</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>14</v>
+        <v>308</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>11</v>
+        <v>98</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F80" t="s">
-        <v>243</v>
+        <v>105</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="3"/>
-      <c r="B81" s="7" t="s">
-        <v>178</v>
+      <c r="B81" t="s">
+        <v>69</v>
       </c>
       <c r="C81" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="D81" t="s">
-        <v>179</v>
+        <v>70</v>
       </c>
       <c r="E81" t="s">
-        <v>180</v>
+        <v>71</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>305</v>
@@ -3030,35 +3033,35 @@
     </row>
     <row r="82" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="3"/>
-      <c r="B82" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F82" t="s">
-        <v>291</v>
+      <c r="B82" t="s">
+        <v>129</v>
+      </c>
+      <c r="C82" t="s">
+        <v>40</v>
+      </c>
+      <c r="D82" t="s">
+        <v>130</v>
+      </c>
+      <c r="E82" t="s">
+        <v>131</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="3"/>
-      <c r="B83" t="s">
-        <v>108</v>
+      <c r="B83" s="7" t="s">
+        <v>27</v>
       </c>
       <c r="C83" t="s">
-        <v>40</v>
-      </c>
-      <c r="D83" t="s">
-        <v>80</v>
-      </c>
-      <c r="E83" t="s">
-        <v>109</v>
+        <v>16</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>305</v>
@@ -3067,88 +3070,88 @@
     <row r="84" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="3"/>
       <c r="B84" t="s">
-        <v>181</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>314</v>
+        <v>45</v>
+      </c>
+      <c r="C84" t="s">
+        <v>24</v>
       </c>
       <c r="D84" t="s">
-        <v>11</v>
+        <v>98</v>
       </c>
       <c r="E84" t="s">
-        <v>182</v>
-      </c>
-      <c r="F84" t="s">
-        <v>292</v>
+        <v>158</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="3"/>
       <c r="B85" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C85" t="s">
-        <v>7</v>
+        <v>176</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>308</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>148</v>
+        <v>8</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="F85" t="s">
-        <v>293</v>
+        <v>177</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="3"/>
       <c r="B86" t="s">
-        <v>53</v>
-      </c>
-      <c r="C86" t="s">
-        <v>16</v>
+        <v>159</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>314</v>
       </c>
       <c r="D86" t="s">
-        <v>54</v>
+        <v>160</v>
       </c>
       <c r="E86" t="s">
-        <v>55</v>
-      </c>
-      <c r="F86" t="s">
-        <v>296</v>
+        <v>161</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="3"/>
-      <c r="B87" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F87" t="s">
-        <v>297</v>
+      <c r="B87" t="s">
+        <v>112</v>
+      </c>
+      <c r="C87" t="s">
+        <v>16</v>
+      </c>
+      <c r="D87" t="s">
+        <v>35</v>
+      </c>
+      <c r="E87" t="s">
+        <v>113</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="3"/>
-      <c r="B88" t="s">
-        <v>3</v>
+      <c r="B88" s="11" t="s">
+        <v>88</v>
       </c>
       <c r="C88" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D88" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="E88" t="s">
-        <v>5</v>
+        <v>89</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>305</v>
@@ -3157,34 +3160,34 @@
     <row r="89" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="3"/>
       <c r="B89" s="2" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="C89" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="F89" t="s">
-        <v>295</v>
+        <v>169</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="3"/>
-      <c r="B90" t="s">
-        <v>93</v>
+      <c r="B90" s="11" t="s">
+        <v>223</v>
       </c>
       <c r="C90" t="s">
-        <v>16</v>
+        <v>309</v>
       </c>
       <c r="D90" t="s">
-        <v>94</v>
+        <v>224</v>
       </c>
       <c r="E90" t="s">
-        <v>95</v>
+        <v>225</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>305</v>
@@ -3193,52 +3196,52 @@
     <row r="91" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="3"/>
       <c r="B91" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
+      </c>
+      <c r="C91" t="s">
+        <v>40</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="F91" t="s">
-        <v>294</v>
+        <v>49</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="3"/>
       <c r="B92" t="s">
-        <v>204</v>
+        <v>6</v>
       </c>
       <c r="C92" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D92" t="s">
-        <v>205</v>
+        <v>8</v>
       </c>
       <c r="E92" t="s">
-        <v>206</v>
+        <v>9</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="5"/>
-      <c r="B93" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>36</v>
+      <c r="A93" s="3"/>
+      <c r="B93" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C93" t="s">
+        <v>16</v>
+      </c>
+      <c r="D93" t="s">
+        <v>25</v>
+      </c>
+      <c r="E93" t="s">
+        <v>65</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>305</v>
@@ -3246,89 +3249,89 @@
     </row>
     <row r="94" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="3"/>
-      <c r="B94" t="s">
-        <v>173</v>
+      <c r="B94" s="11" t="s">
+        <v>178</v>
       </c>
       <c r="C94" t="s">
-        <v>309</v>
+        <v>7</v>
       </c>
       <c r="D94" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="E94" t="s">
-        <v>175</v>
-      </c>
-      <c r="F94" t="s">
-        <v>300</v>
+        <v>180</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="8"/>
-      <c r="B95" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F95" t="s">
-        <v>298</v>
+      <c r="A95" s="3"/>
+      <c r="B95" t="s">
+        <v>108</v>
+      </c>
+      <c r="C95" t="s">
+        <v>40</v>
+      </c>
+      <c r="D95" t="s">
+        <v>80</v>
+      </c>
+      <c r="E95" t="s">
+        <v>109</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="3"/>
       <c r="B96" t="s">
-        <v>127</v>
+        <v>3</v>
       </c>
       <c r="C96" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D96" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="E96" t="s">
-        <v>128</v>
-      </c>
-      <c r="F96" t="s">
-        <v>299</v>
+        <v>5</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="3"/>
-      <c r="B97" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="F97" t="s">
-        <v>304</v>
+      <c r="B97" t="s">
+        <v>93</v>
+      </c>
+      <c r="C97" t="s">
+        <v>16</v>
+      </c>
+      <c r="D97" t="s">
+        <v>94</v>
+      </c>
+      <c r="E97" t="s">
+        <v>95</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="5"/>
+      <c r="A98" s="3"/>
       <c r="B98" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="C98" t="s">
         <v>14</v>
       </c>
       <c r="D98" t="s">
-        <v>231</v>
+        <v>205</v>
       </c>
       <c r="E98" t="s">
-        <v>232</v>
+        <v>206</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>305</v>
@@ -3337,42 +3340,42 @@
     <row r="99" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A99" s="3"/>
       <c r="B99" s="2" t="s">
-        <v>135</v>
+        <v>33</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="F99" t="s">
-        <v>301</v>
+        <v>36</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A100" s="5"/>
-      <c r="B100" s="8" t="s">
-        <v>30</v>
+      <c r="A100" s="3"/>
+      <c r="B100" t="s">
+        <v>226</v>
       </c>
       <c r="C100" t="s">
-        <v>309</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F100" t="s">
-        <v>303</v>
+        <v>14</v>
+      </c>
+      <c r="D100" t="s">
+        <v>231</v>
+      </c>
+      <c r="E100" t="s">
+        <v>232</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>305</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F100">
-    <sortCondition ref="A74:A100"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F74">
+    <sortCondition descending="1" ref="F39:F74"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/kadro/ok.xlsx
+++ b/kadro/ok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kahra\OneDrive\Documents\GitHub\ulkemyanimda.github.io\kadro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51C43CA5-A610-47E7-9263-71E891205286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5B17499-3850-4AE3-8F29-6438F08A4BED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="330">
   <si>
     <t>Ad-Soyad</t>
   </si>
@@ -1275,11 +1275,11 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1610,623 +1610,649 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
-        <v>162</v>
+      <c r="A2" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>163</v>
-      </c>
-      <c r="D2" t="s">
-        <v>164</v>
+        <v>306</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>241</v>
+        <v>300</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
+        <v>132</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>242</v>
+        <v>133</v>
+      </c>
+      <c r="E3" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D4" t="s">
-        <v>123</v>
+      <c r="A4" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="E4" t="s">
-        <v>247</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>39</v>
+        <v>329</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>40</v>
+        <v>312</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>302</v>
+        <v>78</v>
+      </c>
+      <c r="E5" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>196</v>
+        <v>124</v>
       </c>
       <c r="B6" t="s">
-        <v>197</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>198</v>
+        <v>125</v>
       </c>
       <c r="E6" t="s">
-        <v>248</v>
+        <v>296</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="B7" t="s">
-        <v>40</v>
+        <v>93</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>215</v>
+        <v>95</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>243</v>
+        <v>96</v>
+      </c>
+      <c r="E7" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
-        <v>167</v>
+      <c r="A8" t="s">
+        <v>170</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>306</v>
       </c>
       <c r="C8" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D8" t="s">
-        <v>169</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>302</v>
+        <v>172</v>
+      </c>
+      <c r="E8" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="B9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" t="s">
-        <v>187</v>
-      </c>
-      <c r="E9" s="2"/>
+      <c r="A9" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E9" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>187</v>
+        <v>25</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>245</v>
+        <v>181</v>
+      </c>
+      <c r="E10" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>190</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="A11" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C11" t="s">
-        <v>191</v>
-      </c>
-      <c r="D11" t="s">
-        <v>192</v>
+      <c r="C11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="E11" t="s">
-        <v>246</v>
+        <v>294</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
-        <v>315</v>
+      <c r="A12" t="s">
+        <v>51</v>
       </c>
       <c r="B12" t="s">
-        <v>323</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>52</v>
+      </c>
+      <c r="D12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
-        <v>316</v>
+      <c r="A13" s="9" t="s">
+        <v>144</v>
       </c>
       <c r="B13" t="s">
-        <v>324</v>
-      </c>
-      <c r="C13" t="s">
-        <v>25</v>
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E13" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>226</v>
+      <c r="A14" t="s">
+        <v>178</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>244</v>
+      <c r="C14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" t="s">
+        <v>179</v>
+      </c>
+      <c r="E14" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>111</v>
-      </c>
-      <c r="B15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" t="s">
-        <v>112</v>
-      </c>
-      <c r="D15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>302</v>
+      <c r="A15" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="A16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E16" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="B17" t="s">
-        <v>310</v>
-      </c>
-      <c r="C17" t="s">
-        <v>212</v>
-      </c>
-      <c r="D17" t="s">
-        <v>213</v>
+      <c r="C17" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="E17" t="s">
-        <v>250</v>
+        <v>285</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
-        <v>317</v>
+      <c r="A18" t="s">
+        <v>97</v>
       </c>
       <c r="B18" t="s">
-        <v>325</v>
+        <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>191</v>
+        <v>37</v>
+      </c>
+      <c r="D18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E18" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>311</v>
+      <c r="A19" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B19" t="s">
+        <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>302</v>
+        <v>151</v>
+      </c>
+      <c r="E19" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>59</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>311</v>
+        <v>129</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="D20" t="s">
-        <v>61</v>
+        <v>131</v>
       </c>
       <c r="E20" t="s">
-        <v>249</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>141</v>
+        <v>64</v>
       </c>
       <c r="B21" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>142</v>
+        <v>65</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>143</v>
+        <v>66</v>
       </c>
       <c r="E21" t="s">
-        <v>254</v>
+        <v>279</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>239</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
         <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>157</v>
+        <v>18</v>
+      </c>
+      <c r="D22" t="s">
+        <v>19</v>
       </c>
       <c r="E22" t="s">
-        <v>253</v>
+        <v>283</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="10" t="s">
-        <v>152</v>
+      <c r="A23" s="2" t="s">
+        <v>204</v>
       </c>
       <c r="B23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E23" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="B24" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E24" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>147</v>
+      </c>
+      <c r="B25" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>328</v>
-      </c>
-      <c r="B24" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" t="s">
-        <v>37</v>
-      </c>
-      <c r="D24" t="s">
-        <v>38</v>
-      </c>
-      <c r="E24" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="B25" s="2" t="s">
+      <c r="C25" t="s">
+        <v>148</v>
+      </c>
+      <c r="D25" t="s">
+        <v>149</v>
+      </c>
+      <c r="E25" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>46</v>
-      </c>
-      <c r="B26" t="s">
-        <v>308</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="C26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E26" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>209</v>
+      </c>
+      <c r="B27" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" t="s">
         <v>35</v>
       </c>
-      <c r="D26" t="s">
-        <v>47</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>256</v>
+      <c r="D27" t="s">
+        <v>210</v>
+      </c>
+      <c r="E27" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>224</v>
+      <c r="A28" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="B28" t="s">
         <v>7</v>
       </c>
-      <c r="C28" t="s">
-        <v>112</v>
-      </c>
-      <c r="D28" t="s">
-        <v>225</v>
+      <c r="C28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>55</v>
       </c>
       <c r="E28" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>313</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>311</v>
+        <v>184</v>
+      </c>
+      <c r="B29" t="s">
+        <v>14</v>
       </c>
       <c r="C29" t="s">
-        <v>75</v>
+        <v>185</v>
       </c>
       <c r="D29" t="s">
-        <v>76</v>
+        <v>186</v>
       </c>
       <c r="E29" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>305</v>
+        <v>193</v>
+      </c>
+      <c r="B30" t="s">
+        <v>14</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>95</v>
+        <v>194</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>302</v>
+        <v>195</v>
+      </c>
+      <c r="E30" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>56</v>
+      <c r="A31" s="9" t="s">
+        <v>159</v>
       </c>
       <c r="B31" t="s">
-        <v>307</v>
-      </c>
-      <c r="C31" t="s">
-        <v>57</v>
-      </c>
-      <c r="D31" t="s">
-        <v>58</v>
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>161</v>
       </c>
       <c r="E31" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>14</v>
+      <c r="A32" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="B32" t="s">
+        <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>22</v>
+        <v>138</v>
       </c>
       <c r="E32" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>67</v>
+      <c r="A33" s="9" t="s">
+        <v>10</v>
       </c>
       <c r="B33" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E33" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="B34" t="s">
         <v>24</v>
       </c>
-      <c r="C33" t="s">
-        <v>68</v>
-      </c>
-      <c r="D33" t="s">
-        <v>69</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>233</v>
+      <c r="C34" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34" t="s">
+        <v>238</v>
       </c>
       <c r="E34" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>126</v>
+        <v>82</v>
       </c>
       <c r="B35" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="C35" t="s">
-        <v>127</v>
+        <v>83</v>
       </c>
       <c r="D35" t="s">
-        <v>128</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>302</v>
+        <v>84</v>
+      </c>
+      <c r="E35" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="10" t="s">
-        <v>43</v>
+      <c r="A36" s="2" t="s">
+        <v>230</v>
       </c>
       <c r="B36" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>18</v>
+        <v>194</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>44</v>
+        <v>231</v>
       </c>
       <c r="E36" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="5" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B37" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C37" t="s">
-        <v>8</v>
+        <v>135</v>
       </c>
       <c r="D37" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E37" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="10" t="s">
-        <v>27</v>
+      <c r="A38" s="2" t="s">
+        <v>234</v>
       </c>
       <c r="B38" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>28</v>
+        <v>235</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>302</v>
+        <v>236</v>
+      </c>
+      <c r="E38" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>23</v>
+        <v>206</v>
       </c>
       <c r="B39" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C39" t="s">
-        <v>25</v>
+        <v>207</v>
       </c>
       <c r="D39" t="s">
-        <v>26</v>
+        <v>208</v>
       </c>
       <c r="E39" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -2247,759 +2273,782 @@
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="8" t="s">
-        <v>206</v>
+      <c r="A41" t="s">
+        <v>23</v>
       </c>
       <c r="B41" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" t="s">
+        <v>25</v>
+      </c>
+      <c r="D41" t="s">
+        <v>26</v>
+      </c>
+      <c r="E41" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="B42" t="s">
+        <v>40</v>
+      </c>
+      <c r="C42" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" t="s">
+        <v>140</v>
+      </c>
+      <c r="E42" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E43" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C41" t="s">
-        <v>207</v>
-      </c>
-      <c r="D41" t="s">
-        <v>208</v>
-      </c>
-      <c r="E41" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="B42" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="E42" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>134</v>
-      </c>
-      <c r="B43" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" t="s">
-        <v>135</v>
-      </c>
-      <c r="D43" t="s">
-        <v>136</v>
-      </c>
-      <c r="E43" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>45</v>
-      </c>
-      <c r="B44" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" t="s">
-        <v>95</v>
-      </c>
-      <c r="D44" t="s">
-        <v>155</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>302</v>
+      <c r="C44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E44" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="B45" t="s">
+        <v>20</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>194</v>
+        <v>21</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>231</v>
+        <v>22</v>
       </c>
       <c r="E45" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="8" t="s">
-        <v>82</v>
+      <c r="A46" t="s">
+        <v>56</v>
       </c>
       <c r="B46" t="s">
+        <v>307</v>
+      </c>
+      <c r="C46" t="s">
+        <v>57</v>
+      </c>
+      <c r="D46" t="s">
+        <v>58</v>
+      </c>
+      <c r="E46" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C47" t="s">
+        <v>75</v>
+      </c>
+      <c r="D47" t="s">
+        <v>76</v>
+      </c>
+      <c r="E47" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="B48" t="s">
         <v>7</v>
       </c>
-      <c r="C46" t="s">
-        <v>83</v>
-      </c>
-      <c r="D46" t="s">
-        <v>84</v>
-      </c>
-      <c r="E46" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>237</v>
-      </c>
-      <c r="B48" t="s">
-        <v>24</v>
-      </c>
       <c r="C48" t="s">
-        <v>18</v>
+        <v>112</v>
       </c>
       <c r="D48" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="E48" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B49" t="s">
+        <v>217</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="B50" t="s">
         <v>7</v>
       </c>
-      <c r="C49" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E49" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>156</v>
-      </c>
-      <c r="B50" s="2" t="s">
+      <c r="C50" t="s">
+        <v>37</v>
+      </c>
+      <c r="D50" t="s">
+        <v>38</v>
+      </c>
+      <c r="E50" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>239</v>
+      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" t="s">
+        <v>157</v>
+      </c>
+      <c r="E51" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B52" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E52" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="C50" t="s">
-        <v>157</v>
-      </c>
-      <c r="D50" t="s">
-        <v>158</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="B51" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E51" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B52" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" t="s">
-        <v>35</v>
-      </c>
-      <c r="D52" t="s">
-        <v>110</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="B53" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>161</v>
+      <c r="C53" t="s">
+        <v>60</v>
+      </c>
+      <c r="D53" t="s">
+        <v>61</v>
       </c>
       <c r="E53" t="s">
-        <v>272</v>
+        <v>249</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>85</v>
+        <v>211</v>
       </c>
       <c r="B54" t="s">
-        <v>24</v>
+        <v>310</v>
       </c>
       <c r="C54" t="s">
-        <v>35</v>
+        <v>212</v>
       </c>
       <c r="D54" t="s">
-        <v>86</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>302</v>
+        <v>213</v>
+      </c>
+      <c r="E54" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>193</v>
+        <v>79</v>
       </c>
       <c r="B55" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>194</v>
+        <v>80</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>195</v>
+        <v>81</v>
       </c>
       <c r="E55" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>184</v>
-      </c>
-      <c r="B56" t="s">
-        <v>14</v>
-      </c>
-      <c r="C56" t="s">
-        <v>185</v>
-      </c>
-      <c r="D56" t="s">
-        <v>186</v>
-      </c>
-      <c r="E56" t="s">
-        <v>274</v>
+      <c r="A56" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
-        <v>54</v>
+      <c r="A57" t="s">
+        <v>190</v>
       </c>
       <c r="B57" t="s">
-        <v>7</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>55</v>
+        <v>24</v>
+      </c>
+      <c r="C57" t="s">
+        <v>191</v>
+      </c>
+      <c r="D57" t="s">
+        <v>192</v>
       </c>
       <c r="E57" t="s">
-        <v>277</v>
+        <v>246</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>209</v>
+      <c r="A58" s="2" t="s">
+        <v>188</v>
       </c>
       <c r="B58" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" t="s">
-        <v>35</v>
-      </c>
-      <c r="D58" t="s">
-        <v>210</v>
-      </c>
-      <c r="E58" t="s">
-        <v>276</v>
+        <v>40</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>165</v>
+        <v>214</v>
       </c>
       <c r="B59" t="s">
         <v>40</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>31</v>
+        <v>215</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>166</v>
+        <v>216</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>302</v>
+        <v>243</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="B60" t="s">
-        <v>306</v>
+        <v>197</v>
       </c>
       <c r="C60" t="s">
-        <v>221</v>
+        <v>35</v>
       </c>
       <c r="D60" t="s">
-        <v>222</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>302</v>
+        <v>198</v>
+      </c>
+      <c r="E60" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>6</v>
+        <v>121</v>
       </c>
       <c r="B61" t="s">
         <v>7</v>
       </c>
       <c r="C61" t="s">
-        <v>8</v>
+        <v>122</v>
       </c>
       <c r="D61" t="s">
-        <v>9</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>302</v>
+        <v>123</v>
+      </c>
+      <c r="E61" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>311</v>
+        <v>118</v>
+      </c>
+      <c r="B62" t="s">
+        <v>14</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>25</v>
+        <v>119</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E62" t="s">
-        <v>278</v>
+        <v>120</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>147</v>
+      <c r="A63" s="4" t="s">
+        <v>162</v>
       </c>
       <c r="B63" t="s">
         <v>7</v>
       </c>
       <c r="C63" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="D63" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="E63" t="s">
-        <v>280</v>
+        <v>241</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B64" t="s">
+        <v>39</v>
+      </c>
+      <c r="B64" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E64" t="s">
-        <v>282</v>
+        <v>42</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A65" s="7" t="s">
-        <v>318</v>
+      <c r="A65" t="s">
+        <v>167</v>
       </c>
       <c r="B65" t="s">
-        <v>40</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D65" s="2"/>
+        <v>7</v>
+      </c>
+      <c r="C65" t="s">
+        <v>168</v>
+      </c>
+      <c r="D65" t="s">
+        <v>169</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>302</v>
+      </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>62</v>
+        <v>111</v>
       </c>
       <c r="B66" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" t="s">
+        <v>112</v>
+      </c>
+      <c r="D66" t="s">
+        <v>113</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="B68" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A69" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>46</v>
+      </c>
+      <c r="B70" t="s">
+        <v>308</v>
+      </c>
+      <c r="C70" t="s">
+        <v>35</v>
+      </c>
+      <c r="D70" t="s">
+        <v>47</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A71" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>67</v>
+      </c>
+      <c r="B72" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" t="s">
+        <v>68</v>
+      </c>
+      <c r="D72" t="s">
+        <v>69</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A73" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="B73" t="s">
+        <v>40</v>
+      </c>
+      <c r="C73" t="s">
+        <v>127</v>
+      </c>
+      <c r="D73" t="s">
+        <v>128</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B74" t="s">
         <v>16</v>
       </c>
-      <c r="C66" t="s">
-        <v>25</v>
-      </c>
-      <c r="D66" t="s">
-        <v>63</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="B67" t="s">
+      <c r="C74" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B75" t="s">
+        <v>24</v>
+      </c>
+      <c r="C75" t="s">
+        <v>95</v>
+      </c>
+      <c r="D75" t="s">
+        <v>155</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C77" t="s">
+        <v>157</v>
+      </c>
+      <c r="D77" t="s">
+        <v>158</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A78" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B78" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" t="s">
+        <v>35</v>
+      </c>
+      <c r="D78" t="s">
+        <v>110</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B79" t="s">
+        <v>24</v>
+      </c>
+      <c r="C79" t="s">
+        <v>35</v>
+      </c>
+      <c r="D79" t="s">
+        <v>86</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="B80" t="s">
         <v>40</v>
       </c>
-      <c r="C67" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="E67" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>17</v>
-      </c>
-      <c r="B68" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" t="s">
-        <v>18</v>
-      </c>
-      <c r="D68" t="s">
-        <v>19</v>
-      </c>
-      <c r="E68" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B69" t="s">
-        <v>7</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E69" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="B70" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" t="s">
-        <v>130</v>
-      </c>
-      <c r="D70" t="s">
-        <v>131</v>
-      </c>
-      <c r="E70" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="B71" t="s">
-        <v>7</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="E71" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="B72" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" t="s">
-        <v>37</v>
-      </c>
-      <c r="D72" t="s">
-        <v>98</v>
-      </c>
-      <c r="E72" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B73" t="s">
-        <v>7</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E73" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A74" s="9" t="s">
-        <v>319</v>
-      </c>
-      <c r="E74" s="2"/>
-    </row>
-    <row r="75" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E75" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="B76" t="s">
-        <v>7</v>
-      </c>
-      <c r="C76" t="s">
-        <v>176</v>
-      </c>
-      <c r="D76" t="s">
-        <v>177</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E77" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>105</v>
-      </c>
-      <c r="B78" t="s">
-        <v>40</v>
-      </c>
-      <c r="C78" t="s">
-        <v>77</v>
-      </c>
-      <c r="D78" t="s">
-        <v>106</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A79" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="B79" t="s">
-        <v>326</v>
-      </c>
-      <c r="C79" t="s">
-        <v>25</v>
-      </c>
-      <c r="E79" s="2"/>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A80" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="B80" t="s">
-        <v>16</v>
-      </c>
-      <c r="C80" t="s">
-        <v>25</v>
-      </c>
-      <c r="E80" s="2"/>
+      <c r="C80" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>302</v>
+      </c>
     </row>
     <row r="81" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>311</v>
+      <c r="A81" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="B81" t="s">
+        <v>306</v>
       </c>
       <c r="C81" t="s">
-        <v>11</v>
+        <v>221</v>
       </c>
       <c r="D81" t="s">
-        <v>179</v>
-      </c>
-      <c r="E81" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="6" t="s">
-        <v>144</v>
+        <v>222</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>6</v>
       </c>
       <c r="B82" t="s">
         <v>7</v>
       </c>
-      <c r="C82" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="E82" t="s">
-        <v>290</v>
+      <c r="C82" t="s">
+        <v>8</v>
+      </c>
+      <c r="D82" t="s">
+        <v>9</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B83" t="s">
         <v>16</v>
       </c>
       <c r="C83" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="D83" t="s">
-        <v>53</v>
-      </c>
-      <c r="E83" t="s">
-        <v>293</v>
+        <v>63</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A84" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E84" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A84" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="B84" t="s">
+        <v>7</v>
+      </c>
+      <c r="C84" t="s">
+        <v>176</v>
+      </c>
+      <c r="D84" t="s">
+        <v>177</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
+        <v>105</v>
+      </c>
+      <c r="B85" t="s">
+        <v>40</v>
+      </c>
+      <c r="C85" t="s">
+        <v>77</v>
+      </c>
+      <c r="D85" t="s">
+        <v>106</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="5" t="s">
         <v>3</v>
-      </c>
-      <c r="B85" t="s">
-        <v>16</v>
-      </c>
-      <c r="C85" t="s">
-        <v>4</v>
-      </c>
-      <c r="D85" t="s">
-        <v>5</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A86" s="2" t="s">
-        <v>180</v>
       </c>
       <c r="B86" t="s">
         <v>16</v>
       </c>
-      <c r="C86" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="E86" t="s">
-        <v>292</v>
+      <c r="C86" t="s">
+        <v>4</v>
+      </c>
+      <c r="D86" t="s">
+        <v>5</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
@@ -3020,206 +3069,186 @@
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A88" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="E88" t="s">
-        <v>291</v>
+      <c r="A88" t="s">
+        <v>201</v>
+      </c>
+      <c r="B88" t="s">
+        <v>14</v>
+      </c>
+      <c r="C88" t="s">
+        <v>202</v>
+      </c>
+      <c r="D88" t="s">
+        <v>203</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
-        <v>201</v>
-      </c>
-      <c r="B89" t="s">
+      <c r="A89" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>223</v>
+      </c>
+      <c r="B90" t="s">
         <v>14</v>
       </c>
-      <c r="C89" t="s">
-        <v>202</v>
-      </c>
-      <c r="D89" t="s">
-        <v>203</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A90" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>36</v>
+      <c r="C90" t="s">
+        <v>228</v>
+      </c>
+      <c r="D90" t="s">
+        <v>229</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
-        <v>170</v>
+      <c r="A91" s="7" t="s">
+        <v>314</v>
       </c>
       <c r="B91" t="s">
-        <v>306</v>
+        <v>7</v>
       </c>
       <c r="C91" t="s">
-        <v>171</v>
-      </c>
-      <c r="D91" t="s">
-        <v>172</v>
-      </c>
-      <c r="E91" t="s">
-        <v>297</v>
+        <v>187</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A92" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E92" t="s">
-        <v>295</v>
+      <c r="A92" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="B92" t="s">
+        <v>323</v>
+      </c>
+      <c r="C92" t="s">
+        <v>25</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
-        <v>124</v>
+      <c r="A93" s="7" t="s">
+        <v>316</v>
       </c>
       <c r="B93" t="s">
-        <v>7</v>
+        <v>324</v>
       </c>
       <c r="C93" t="s">
         <v>25</v>
       </c>
-      <c r="D93" t="s">
-        <v>125</v>
-      </c>
-      <c r="E93" t="s">
-        <v>296</v>
+      <c r="E93" s="2" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="B94" t="s">
+        <v>325</v>
+      </c>
+      <c r="C94" t="s">
+        <v>191</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A95" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="B95" t="s">
+        <v>40</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D95" s="2"/>
+      <c r="E95" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A96" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="B96" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" t="s">
+        <v>25</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A97" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="B97" t="s">
+        <v>326</v>
+      </c>
+      <c r="C97" t="s">
+        <v>25</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A98" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="B98" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" t="s">
+        <v>25</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A99" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B99" t="s">
         <v>40</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C99" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A95" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E95" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A96" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E96" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
-        <v>223</v>
-      </c>
-      <c r="B97" t="s">
-        <v>14</v>
-      </c>
-      <c r="C97" t="s">
-        <v>228</v>
-      </c>
-      <c r="D97" t="s">
-        <v>229</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A98" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="E98" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A99" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B99" t="s">
-        <v>306</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E99" t="s">
-        <v>300</v>
+      <c r="E99" s="2" t="s">
+        <v>302</v>
       </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E100">
-    <sortCondition ref="A1:A100"/>
+    <sortCondition descending="1" ref="A1:A100"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3227,12 +3256,598 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8FC3ADF-B568-418D-9CFC-DAC57AE67DCA}">
-  <dimension ref="B100:B143"/>
+  <dimension ref="A1:E143"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="41.44140625" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" t="s">
+        <v>308</v>
+      </c>
+      <c r="C7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="B10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" t="s">
+        <v>127</v>
+      </c>
+      <c r="D10" t="s">
+        <v>128</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" t="s">
+        <v>95</v>
+      </c>
+      <c r="D12" t="s">
+        <v>155</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C14" t="s">
+        <v>157</v>
+      </c>
+      <c r="D14" t="s">
+        <v>158</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" t="s">
+        <v>110</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" t="s">
+        <v>86</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="B17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="B18" t="s">
+        <v>306</v>
+      </c>
+      <c r="C18" t="s">
+        <v>221</v>
+      </c>
+      <c r="D18" t="s">
+        <v>222</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>62</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" t="s">
+        <v>63</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" t="s">
+        <v>176</v>
+      </c>
+      <c r="D21" t="s">
+        <v>177</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>105</v>
+      </c>
+      <c r="B22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" t="s">
+        <v>77</v>
+      </c>
+      <c r="D22" t="s">
+        <v>106</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>90</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="s">
+        <v>91</v>
+      </c>
+      <c r="D24" t="s">
+        <v>92</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>201</v>
+      </c>
+      <c r="B25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" t="s">
+        <v>202</v>
+      </c>
+      <c r="D25" t="s">
+        <v>203</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>223</v>
+      </c>
+      <c r="B27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" t="s">
+        <v>228</v>
+      </c>
+      <c r="D27" t="s">
+        <v>229</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A28" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="B28" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" t="s">
+        <v>187</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A29" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="B29" t="s">
+        <v>323</v>
+      </c>
+      <c r="C29" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="B30" t="s">
+        <v>324</v>
+      </c>
+      <c r="C30" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A31" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="B31" t="s">
+        <v>325</v>
+      </c>
+      <c r="C31" t="s">
+        <v>191</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A32" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="B32" t="s">
+        <v>40</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A33" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="s">
+        <v>25</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A34" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="B34" t="s">
+        <v>326</v>
+      </c>
+      <c r="C34" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="s">
+        <v>25</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A36" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="B36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C36" t="s">
+        <v>327</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
     <row r="100" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="101" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B101" s="3"/>

--- a/kadro/ok.xlsx
+++ b/kadro/ok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kahra\OneDrive\Documents\GitHub\ulkemyanimda.github.io\kadro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D89046A-4976-4E2D-AA68-103FFBBC9E7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ACE535B-4F1A-437A-8C15-A73F58A7D039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -671,14 +671,6 @@
     <t xml:space="preserve">İstanbul </t>
   </si>
   <si>
-    <t>Tamam, verdiğin eklemelerle samimi, hedef odaklı ve kapsamlı bir tanıtım yazısı hazırladım. Yaklaşık 150 kelime:
-⸻
-Ben Aslı Uysal Cevgin. 20 yıldır Türkçe öğretmenliği yapıyorum ve öğrencilerin öğrenme süreçlerini merak, etkileşim ve anlam üzerine inşa etmeyi amaçlıyorum. Şu anda Ülkem Yanımda platformunda, İskandinav ülkelerindeki Türk öğrencilerle çok keyif aldığım dersler yürütüyorum. Onlardan ben de çok şey öğreniyorum. 
-Eğitim yaklaşımımı desteklemek için yaratıcı drama, eTwinning projeleri ve etkileşim odaklı yöntemlerle çalışıyorum. Ayrıca, “İğne Deliğinden Dünya” ve “Etkileşim Odaklı Disiplinlerarası Oyunlar” kitaplarının yazarlarından biriyim. Eğitsel oyunlar ve oyunlaştırma üzerine çalışmayı ve içerik geliştirmeyi özellikle seviyorum.
-Derslerimde amacım, öğrencilerin bilgiyi sorgulamalarını, kendi bakış açılarını geliştirmelerini ve öğrenmeyi aktif hâle getirmelerini sağlamak. Her öğrencinin öğrenme yolculuğunu anlamlı ve keşif odaklı hâle getirmek temel hedefim.
-Günümüzde dijital ortamların hem besleyen hem de dikkat edilmesi gereken alanlar olduğunu düşünüyorum. Bu düşüncelerimden hareketle eleştirel dijital okuryazarlık doktora araştırmama devam ediyorum.</t>
-  </si>
-  <si>
     <t>Hüseyin Pektaş</t>
   </si>
   <si>
@@ -831,311 +823,317 @@
     <t xml:space="preserve">Manisa </t>
   </si>
   <si>
-    <t>23.12.2005 tarihinde  göreve başladım.Şu anda Alaşehir  de Gümüşçay Şehit Mehmet Yalçın İlkokulu’nda görev yapmaktayım.2026 ocak ayında  mesleğimde 20 seneyi doldurduğum için başöğretmen oldum. 
+    <t>Gülendam Ünal</t>
+  </si>
+  <si>
+    <t>Gazi Ünv. mezunu,15 yıllık Türkçe öğretmeniyim.Drama, Doğa Pedagojisi,Yabancılara Türkçe Öğrt. ve Dijital Beceriler uzmanıyım.Bursa YEĞİTEK’te Dijital Ekosistem Proje Kolaylaştırıcısı olarak çalışmaktayım.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cennet Uzunoğlu </t>
+  </si>
+  <si>
+    <t>./img/aacetinkaya.jpg</t>
+  </si>
+  <si>
+    <t>./img/aari.jpg</t>
+  </si>
+  <si>
+    <t>./img/abozat.jpg</t>
+  </si>
+  <si>
+    <t>./img/adurur.jpg</t>
+  </si>
+  <si>
+    <t>./img/afuttu.jpg</t>
+  </si>
+  <si>
+    <t>./img/agokmen.jpg</t>
+  </si>
+  <si>
+    <t>./img/auysal.jpg</t>
+  </si>
+  <si>
+    <t>./img/ayalcinkaya.jpg</t>
+  </si>
+  <si>
+    <t>./img/azoba.jpg</t>
+  </si>
+  <si>
+    <t>./img/berkmen.jpg</t>
+  </si>
+  <si>
+    <t>./img/bodemir.jpg</t>
+  </si>
+  <si>
+    <t>./img/btorgul.jpg</t>
+  </si>
+  <si>
+    <t>./img/csakir.jpg</t>
+  </si>
+  <si>
+    <t>./img/cuzunoglu.jpg</t>
+  </si>
+  <si>
+    <t>./img/cyalcin.jpg</t>
+  </si>
+  <si>
+    <t>./img/dbsekin.jpg</t>
+  </si>
+  <si>
+    <t>./img/dtop.jpg</t>
+  </si>
+  <si>
+    <t>./img/ederoglu.jpg</t>
+  </si>
+  <si>
+    <t>./img/edogan.jpg</t>
+  </si>
+  <si>
+    <t>./img/eergin.jpg</t>
+  </si>
+  <si>
+    <t>./img/eerol.jpg</t>
+  </si>
+  <si>
+    <t>./img/eertas.jpg</t>
+  </si>
+  <si>
+    <t>./img/enigar.jpg</t>
+  </si>
+  <si>
+    <t>./img/evrendogan.jpg</t>
+  </si>
+  <si>
+    <t>./img/eyardimci.jpg</t>
+  </si>
+  <si>
+    <t>./img/febilir.jpg</t>
+  </si>
+  <si>
+    <t>./img/ffici.jpg</t>
+  </si>
+  <si>
+    <t>./img/fnukte.jpg</t>
+  </si>
+  <si>
+    <t>./img/fyasa.jpg</t>
+  </si>
+  <si>
+    <t>./img/gakpinar.jpg</t>
+  </si>
+  <si>
+    <t>./img/gunal.jpg</t>
+  </si>
+  <si>
+    <t>./img/gyalman.jpg</t>
+  </si>
+  <si>
+    <t>./img/hersin.jpg</t>
+  </si>
+  <si>
+    <t>./img/hpektas.jpg</t>
+  </si>
+  <si>
+    <t>./img/hyanci.jpg</t>
+  </si>
+  <si>
+    <t>./img/hyildiz.jpg</t>
+  </si>
+  <si>
+    <t>./img/ierk.jpg</t>
+  </si>
+  <si>
+    <t>./img/isanli.jpg</t>
+  </si>
+  <si>
+    <t>./img/lmeshur.jpg</t>
+  </si>
+  <si>
+    <t>./img/matli.jpg</t>
+  </si>
+  <si>
+    <t>./img/mcoskun.jpg</t>
+  </si>
+  <si>
+    <t>./img/meavci.jpg</t>
+  </si>
+  <si>
+    <t>./img/mkutlu.jpg</t>
+  </si>
+  <si>
+    <t>./img/mnazli.jpg</t>
+  </si>
+  <si>
+    <t>./img/myesil.jpg</t>
+  </si>
+  <si>
+    <t>./img/naydin.jpg</t>
+  </si>
+  <si>
+    <t>./img/nayhan.jpg</t>
+  </si>
+  <si>
+    <t>./img/ncetin.jpg</t>
+  </si>
+  <si>
+    <t>./img/okocabiyik.jpg</t>
+  </si>
+  <si>
+    <t>./img/oyucehunkar.jpg</t>
+  </si>
+  <si>
+    <t>./img/pince.jpg</t>
+  </si>
+  <si>
+    <t>./img/sacikgoz.jpg</t>
+  </si>
+  <si>
+    <t>./img/sdemirel.jpg</t>
+  </si>
+  <si>
+    <t>./img/sgokceli.jpg</t>
+  </si>
+  <si>
+    <t>./img/ssaydemir.jpg</t>
+  </si>
+  <si>
+    <t>./img/ucanpolat.jpg</t>
+  </si>
+  <si>
+    <t>./img/uguclu.jpg</t>
+  </si>
+  <si>
+    <t>./img/uoktay.jpg</t>
+  </si>
+  <si>
+    <t>./img/ziuzun.jpg</t>
+  </si>
+  <si>
+    <t>./img/ztaltindis.jpg</t>
+  </si>
+  <si>
+    <t>./img/zyildirim.jpg</t>
+  </si>
+  <si>
+    <t>./img/zyilmaz.jpg</t>
+  </si>
+  <si>
+    <t>./img/uy.jpg</t>
+  </si>
+  <si>
+    <t>foto</t>
+  </si>
+  <si>
+    <t>hayat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Almanca </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Din Kültürü ve Ahlâk Bilgisi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fen Bilimleri  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Görsel Sanatlar </t>
+  </si>
+  <si>
+    <t xml:space="preserve">İlköğretim Matematik </t>
+  </si>
+  <si>
+    <t>Müzik</t>
+  </si>
+  <si>
+    <t>Okul Öncesi</t>
+  </si>
+  <si>
+    <t>Sınıf Öğretmeni/Özel Yetenekliler Öğretmeni</t>
+  </si>
+  <si>
+    <t>Edanur DOĞAN</t>
+  </si>
+  <si>
+    <t>Asiye AKANSU</t>
+  </si>
+  <si>
+    <t>Asuman GÜNER</t>
+  </si>
+  <si>
+    <t>Ayşe ETBAŞ DİNDAR</t>
+  </si>
+  <si>
+    <t>Berrin BAYBURT</t>
+  </si>
+  <si>
+    <t>Meryem YÜCEL</t>
+  </si>
+  <si>
+    <t>Nilüfer BALABAN</t>
+  </si>
+  <si>
+    <t>Oya KAÇAR</t>
+  </si>
+  <si>
+    <t>Oya UYSAL</t>
+  </si>
+  <si>
+    <t>Yeşim OĞUL</t>
+  </si>
+  <si>
+    <t>İHL Meslek Öğretmeni</t>
+  </si>
+  <si>
+    <t>Bilişim Teknolojileri</t>
+  </si>
+  <si>
+    <t>Sosyal Bilgiler</t>
+  </si>
+  <si>
+    <t>Beden Eğitimi</t>
+  </si>
+  <si>
+    <t>Trabzon</t>
+  </si>
+  <si>
+    <t>Çiğdem Şakır</t>
+  </si>
+  <si>
+    <t>Zehra TOPAL ALTINDİŞ</t>
+  </si>
+  <si>
+    <t>Aydın</t>
+  </si>
+  <si>
+    <t>Tunceli</t>
+  </si>
+  <si>
+    <t>Kütahya</t>
+  </si>
+  <si>
+    <t>Elazığ</t>
+  </si>
+  <si>
+    <t>Burdur</t>
+  </si>
+  <si>
+    <t>Bolu</t>
+  </si>
+  <si>
+    <t>Bilecik</t>
+  </si>
+  <si>
+    <t>2005 yılında  göreve başladım.Şu anda Alaşehir  de Gümüşçay Şehit Mehmet Yalçın İlkokulu’nda görev yapmaktayım.2026 ocak ayında  mesleğimde 20 seneyi doldurduğum için başöğretmen oldum. 
 2016 yılında Özel Yetenekliler Destek Eğitim Odası Eğitici Eğitimi programını başarıyla tamamlayarak Formatör unvanını aldım. Bu kapsamda, Alaşehir ve Sarıgöl ilçelerinde görev yapan öğretmenlerimize yönelik hizmet içi eğitimler düzenleyerek; özel yetenekli bireylerin tanılama sonrası eğitim süreçlerinin yapılandırılması ve müfredat farklılaştırma teknikleri konularında uzman rehberlik sundum.
 Milli Eğitim Bakanlığı ve TAZOF iş birliği kapsamındaki eğitim süreçlerini yakından takip ederek 1. ve 2. Kademe Zeka Oyunları Eğitmenlik sertifikalarımı tamamladım. 2018 yılından bu yana düzenlenen TAZOF turnuvalarında hem öğrenci yetiştirerek okulumuzun en iyi şekilde temsil edilmesini sağladım hem de resmi hakem olarak görev aldım. Okulumuzun il ve ilçe düzeyindeki müsabakalarda düzenli dereceler elde etmesinde aktif rol oynayarak, başarı grafiğimizi istikrarlı hale getirdim. Özellikle köy okullarında eğitim gören öğrencilerimizin bilişsel becerilerini zeka oyunlarıyla geliştirmek ve hayata karşı farkındalıklarını yükseltmek, mesleki misyonumun temelini oluşturmaktadır.
 Uluslararası eğitim vizyonum doğrultusunda, 2024-2025 eğitim döneminde "Ülkem Yanımda" projesi kapsamında İskandinavya ve Bulgaristan bölgelerindeki Türk soylu öğrencilere yönelik dil ve kültür derslerini başarıyla yürüttüm. 2025-2026 döneminde ise Amerika grubu öğrencileriyle çalışmalarımı sürdürerek, farklı coğrafyalardaki öğrencilerin kültürel aidiyetlerini güçlendiren tematik içerikler hazırlıyor ve uyguluyorum. Farklı yaş ve seviye gruplarıyla çalışma konusundaki esnekliğimle, müfredat geliştirme ve içerik hazırlama süreçlerinde aktif rol alarak soydaşlarımızın kültürel bağlarını güçlendirmeyi hedefliyorum.
 "Eğitimin hayatın her alanına nüfuz ettiğine olan inancımla; 'öğrenmenin öğrencisi olmayı' mesleki gelişimimin merkezine koyuyorum. Sürekli gelişimi ve güncel eğitim metodolojilerini takip etmeyi, hem kendimi hem de öğrencilerimi ileriye taşımanın temel anahtarı olarak görüyorum. Dinamik bir öğrenme kültürü içerisinde, edindiğim bilgi ve tecrübeyi aktarma motivasyonu yüksek bir eğitimciyim."</t>
   </si>
   <si>
-    <t>Gülendam Ünal</t>
-  </si>
-  <si>
-    <t>Gazi Ünv. mezunu,15 yıllık Türkçe öğretmeniyim.Drama, Doğa Pedagojisi,Yabancılara Türkçe Öğrt. ve Dijital Beceriler uzmanıyım.Bursa YEĞİTEK’te Dijital Ekosistem Proje Kolaylaştırıcısı olarak çalışmaktayım.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cennet Uzunoğlu </t>
-  </si>
-  <si>
-    <t>./img/aacetinkaya.jpg</t>
-  </si>
-  <si>
-    <t>./img/aari.jpg</t>
-  </si>
-  <si>
-    <t>./img/abozat.jpg</t>
-  </si>
-  <si>
-    <t>./img/adurur.jpg</t>
-  </si>
-  <si>
-    <t>./img/afuttu.jpg</t>
-  </si>
-  <si>
-    <t>./img/agokmen.jpg</t>
-  </si>
-  <si>
-    <t>./img/auysal.jpg</t>
-  </si>
-  <si>
-    <t>./img/ayalcinkaya.jpg</t>
-  </si>
-  <si>
-    <t>./img/azoba.jpg</t>
-  </si>
-  <si>
-    <t>./img/berkmen.jpg</t>
-  </si>
-  <si>
-    <t>./img/bodemir.jpg</t>
-  </si>
-  <si>
-    <t>./img/btorgul.jpg</t>
-  </si>
-  <si>
-    <t>./img/csakir.jpg</t>
-  </si>
-  <si>
-    <t>./img/cuzunoglu.jpg</t>
-  </si>
-  <si>
-    <t>./img/cyalcin.jpg</t>
-  </si>
-  <si>
-    <t>./img/dbsekin.jpg</t>
-  </si>
-  <si>
-    <t>./img/dtop.jpg</t>
-  </si>
-  <si>
-    <t>./img/ederoglu.jpg</t>
-  </si>
-  <si>
-    <t>./img/edogan.jpg</t>
-  </si>
-  <si>
-    <t>./img/eergin.jpg</t>
-  </si>
-  <si>
-    <t>./img/eerol.jpg</t>
-  </si>
-  <si>
-    <t>./img/eertas.jpg</t>
-  </si>
-  <si>
-    <t>./img/enigar.jpg</t>
-  </si>
-  <si>
-    <t>./img/evrendogan.jpg</t>
-  </si>
-  <si>
-    <t>./img/eyardimci.jpg</t>
-  </si>
-  <si>
-    <t>./img/febilir.jpg</t>
-  </si>
-  <si>
-    <t>./img/ffici.jpg</t>
-  </si>
-  <si>
-    <t>./img/fnukte.jpg</t>
-  </si>
-  <si>
-    <t>./img/fyasa.jpg</t>
-  </si>
-  <si>
-    <t>./img/gakpinar.jpg</t>
-  </si>
-  <si>
-    <t>./img/gunal.jpg</t>
-  </si>
-  <si>
-    <t>./img/gyalman.jpg</t>
-  </si>
-  <si>
-    <t>./img/hersin.jpg</t>
-  </si>
-  <si>
-    <t>./img/hpektas.jpg</t>
-  </si>
-  <si>
-    <t>./img/hyanci.jpg</t>
-  </si>
-  <si>
-    <t>./img/hyildiz.jpg</t>
-  </si>
-  <si>
-    <t>./img/ierk.jpg</t>
-  </si>
-  <si>
-    <t>./img/isanli.jpg</t>
-  </si>
-  <si>
-    <t>./img/lmeshur.jpg</t>
-  </si>
-  <si>
-    <t>./img/matli.jpg</t>
-  </si>
-  <si>
-    <t>./img/mcoskun.jpg</t>
-  </si>
-  <si>
-    <t>./img/meavci.jpg</t>
-  </si>
-  <si>
-    <t>./img/mkutlu.jpg</t>
-  </si>
-  <si>
-    <t>./img/mnazli.jpg</t>
-  </si>
-  <si>
-    <t>./img/myesil.jpg</t>
-  </si>
-  <si>
-    <t>./img/naydin.jpg</t>
-  </si>
-  <si>
-    <t>./img/nayhan.jpg</t>
-  </si>
-  <si>
-    <t>./img/ncetin.jpg</t>
-  </si>
-  <si>
-    <t>./img/okocabiyik.jpg</t>
-  </si>
-  <si>
-    <t>./img/oyucehunkar.jpg</t>
-  </si>
-  <si>
-    <t>./img/pince.jpg</t>
-  </si>
-  <si>
-    <t>./img/sacikgoz.jpg</t>
-  </si>
-  <si>
-    <t>./img/sdemirel.jpg</t>
-  </si>
-  <si>
-    <t>./img/sgokceli.jpg</t>
-  </si>
-  <si>
-    <t>./img/ssaydemir.jpg</t>
-  </si>
-  <si>
-    <t>./img/ucanpolat.jpg</t>
-  </si>
-  <si>
-    <t>./img/uguclu.jpg</t>
-  </si>
-  <si>
-    <t>./img/uoktay.jpg</t>
-  </si>
-  <si>
-    <t>./img/ziuzun.jpg</t>
-  </si>
-  <si>
-    <t>./img/ztaltindis.jpg</t>
-  </si>
-  <si>
-    <t>./img/zyildirim.jpg</t>
-  </si>
-  <si>
-    <t>./img/zyilmaz.jpg</t>
-  </si>
-  <si>
-    <t>./img/uy.jpg</t>
-  </si>
-  <si>
-    <t>foto</t>
-  </si>
-  <si>
-    <t>hayat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Almanca </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Din Kültürü ve Ahlâk Bilgisi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fen Bilimleri  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Görsel Sanatlar </t>
-  </si>
-  <si>
-    <t xml:space="preserve">İlköğretim Matematik </t>
-  </si>
-  <si>
-    <t>Müzik</t>
-  </si>
-  <si>
-    <t>Okul Öncesi</t>
-  </si>
-  <si>
-    <t>Sınıf Öğretmeni/Özel Yetenekliler Öğretmeni</t>
-  </si>
-  <si>
-    <t>Edanur DOĞAN</t>
-  </si>
-  <si>
-    <t>Asiye AKANSU</t>
-  </si>
-  <si>
-    <t>Asuman GÜNER</t>
-  </si>
-  <si>
-    <t>Ayşe ETBAŞ DİNDAR</t>
-  </si>
-  <si>
-    <t>Berrin BAYBURT</t>
-  </si>
-  <si>
-    <t>Meryem YÜCEL</t>
-  </si>
-  <si>
-    <t>Nilüfer BALABAN</t>
-  </si>
-  <si>
-    <t>Oya KAÇAR</t>
-  </si>
-  <si>
-    <t>Oya UYSAL</t>
-  </si>
-  <si>
-    <t>Yeşim OĞUL</t>
-  </si>
-  <si>
-    <t>İHL Meslek Öğretmeni</t>
-  </si>
-  <si>
-    <t>Bilişim Teknolojileri</t>
-  </si>
-  <si>
-    <t>Sosyal Bilgiler</t>
-  </si>
-  <si>
-    <t>Beden Eğitimi</t>
-  </si>
-  <si>
-    <t>Trabzon</t>
-  </si>
-  <si>
-    <t>Çiğdem Şakır</t>
-  </si>
-  <si>
-    <t>Zehra TOPAL ALTINDİŞ</t>
-  </si>
-  <si>
-    <t>Aydın</t>
-  </si>
-  <si>
-    <t>Tunceli</t>
-  </si>
-  <si>
-    <t>Kütahya</t>
-  </si>
-  <si>
-    <t>Elazığ</t>
-  </si>
-  <si>
-    <t>Burdur</t>
-  </si>
-  <si>
-    <t>Bolu</t>
-  </si>
-  <si>
-    <t>Bilecik</t>
+    <t>Ben Aslı Uysal Cevgin. 20 yıldır Türkçe öğretmenliği yapıyorum ve öğrencilerin öğrenme süreçlerini merak, etkileşim ve anlam üzerine inşa etmeyi amaçlıyorum. Şu anda Ülkem Yanımda platformunda, İskandinav ülkelerindeki Türk öğrencilerle çok keyif aldığım dersler yürütüyorum. Onlardan ben de çok şey öğreniyorum. 
+Eğitim yaklaşımımı desteklemek için yaratıcı drama, eTwinning projeleri ve etkileşim odaklı yöntemlerle çalışıyorum. Ayrıca, “İğne Deliğinden Dünya” ve “Etkileşim Odaklı Disiplinlerarası Oyunlar” kitaplarının yazarlarından biriyim. Eğitsel oyunlar ve oyunlaştırma üzerine çalışmayı ve içerik geliştirmeyi özellikle seviyorum.
+Derslerimde amacım, öğrencilerin bilgiyi sorgulamalarını, kendi bakış açılarını geliştirmelerini ve öğrenmeyi aktif hâle getirmelerini sağlamak. Her öğrencinin öğrenme yolculuğunu anlamlı ve keşif odaklı hâle getirmek temel hedefim.
+Günümüzde dijital ortamların hem besleyen hem de dikkat edilmesi gereken alanlar olduğunu düşünüyorum. Bu düşüncelerimden hareketle eleştirel dijital okuryazarlık doktora araştırmama devam ediyorum.</t>
   </si>
 </sst>
 </file>
@@ -1224,7 +1222,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1232,6 +1230,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1559,10 +1563,10 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -1573,7 +1577,7 @@
         <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>30</v>
@@ -1582,7 +1586,7 @@
         <v>31</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1602,7 +1606,7 @@
         <v>126</v>
       </c>
       <c r="F3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -1622,7 +1626,7 @@
         <v>112</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1630,10 +1634,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C5" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D5" t="s">
         <v>73</v>
@@ -1642,7 +1646,7 @@
         <v>74</v>
       </c>
       <c r="F5" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -1662,7 +1666,7 @@
         <v>118</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -1682,7 +1686,7 @@
         <v>91</v>
       </c>
       <c r="F7" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -1693,16 +1697,16 @@
         <v>160</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>161</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -1710,7 +1714,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C9" t="s">
         <v>23</v>
@@ -1719,10 +1723,10 @@
         <v>90</v>
       </c>
       <c r="E9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -1742,7 +1746,7 @@
         <v>170</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -1762,7 +1766,7 @@
         <v>70</v>
       </c>
       <c r="F11" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -1782,7 +1786,7 @@
         <v>52</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -1802,7 +1806,7 @@
         <v>138</v>
       </c>
       <c r="F13" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -1813,7 +1817,7 @@
         <v>167</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>11</v>
@@ -1822,7 +1826,7 @@
         <v>168</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -1833,7 +1837,7 @@
         <v>47</v>
       </c>
       <c r="C15" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D15" t="s">
         <v>48</v>
@@ -1842,7 +1846,7 @@
         <v>49</v>
       </c>
       <c r="F15" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -1862,7 +1866,7 @@
         <v>15</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -1882,7 +1886,7 @@
         <v>68</v>
       </c>
       <c r="F17" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -1902,7 +1906,7 @@
         <v>93</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -1922,7 +1926,7 @@
         <v>142</v>
       </c>
       <c r="F19" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -1942,7 +1946,7 @@
         <v>124</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -1962,7 +1966,7 @@
         <v>63</v>
       </c>
       <c r="F21" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -1982,7 +1986,7 @@
         <v>19</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -1990,7 +1994,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C23" t="s">
         <v>39</v>
@@ -1999,10 +2003,10 @@
         <v>73</v>
       </c>
       <c r="E23" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F23" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -2022,7 +2026,7 @@
         <v>103</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -2042,7 +2046,7 @@
         <v>140</v>
       </c>
       <c r="F25" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -2053,7 +2057,7 @@
         <v>98</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>24</v>
@@ -2062,7 +2066,7 @@
         <v>99</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -2070,7 +2074,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C27" t="s">
         <v>23</v>
@@ -2079,10 +2083,10 @@
         <v>34</v>
       </c>
       <c r="E27" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F27" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -2102,7 +2106,7 @@
         <v>54</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -2122,7 +2126,7 @@
         <v>175</v>
       </c>
       <c r="F29" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -2130,7 +2134,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>14</v>
@@ -2139,10 +2143,10 @@
         <v>34</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -2162,7 +2166,7 @@
         <v>151</v>
       </c>
       <c r="F31" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
@@ -2182,7 +2186,7 @@
         <v>131</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
@@ -2202,7 +2206,7 @@
         <v>12</v>
       </c>
       <c r="F33" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -2210,7 +2214,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>23</v>
@@ -2219,10 +2223,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -2242,7 +2246,7 @@
         <v>80</v>
       </c>
       <c r="F35" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -2250,7 +2254,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>14</v>
@@ -2259,10 +2263,10 @@
         <v>34</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -2282,27 +2286,27 @@
         <v>129</v>
       </c>
       <c r="F37" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>320</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -2310,19 +2314,19 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C39" t="s">
         <v>14</v>
       </c>
       <c r="D39" t="s">
+        <v>194</v>
+      </c>
+      <c r="E39" t="s">
         <v>195</v>
       </c>
-      <c r="E39" t="s">
-        <v>196</v>
-      </c>
       <c r="F39" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -2342,7 +2346,7 @@
         <v>172</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -2362,7 +2366,7 @@
         <v>25</v>
       </c>
       <c r="F41" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -2382,7 +2386,7 @@
         <v>133</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -2402,7 +2406,7 @@
         <v>43</v>
       </c>
       <c r="F43" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -2410,7 +2414,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>14</v>
@@ -2419,10 +2423,10 @@
         <v>24</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -2436,13 +2440,13 @@
         <v>14</v>
       </c>
       <c r="D45" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E45" t="s">
         <v>21</v>
       </c>
       <c r="F45" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -2453,7 +2457,7 @@
         <v>55</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>56</v>
@@ -2462,7 +2466,7 @@
         <v>57</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -2470,10 +2474,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C47" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D47" t="s">
         <v>71</v>
@@ -2482,7 +2486,7 @@
         <v>72</v>
       </c>
       <c r="F47" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -2490,7 +2494,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>7</v>
@@ -2499,10 +2503,10 @@
         <v>107</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
@@ -2510,19 +2514,19 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
+        <v>203</v>
+      </c>
+      <c r="C49" t="s">
+        <v>288</v>
+      </c>
+      <c r="D49" t="s">
         <v>204</v>
       </c>
-      <c r="C49" t="s">
-        <v>290</v>
-      </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
         <v>205</v>
       </c>
-      <c r="E49" t="s">
-        <v>206</v>
-      </c>
       <c r="F49" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -2530,7 +2534,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>7</v>
@@ -2542,7 +2546,7 @@
         <v>37</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
@@ -2550,7 +2554,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C51" t="s">
         <v>16</v>
@@ -2559,7 +2563,7 @@
         <v>147</v>
       </c>
       <c r="F51" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
@@ -2573,13 +2577,13 @@
         <v>7</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>135</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
@@ -2590,16 +2594,16 @@
         <v>58</v>
       </c>
       <c r="C53" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E53" t="s">
         <v>59</v>
       </c>
       <c r="F53" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
@@ -2607,19 +2611,19 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>90</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
@@ -2639,7 +2643,7 @@
         <v>77</v>
       </c>
       <c r="F55" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
@@ -2647,22 +2651,22 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
@@ -2675,11 +2679,11 @@
       <c r="D57" t="s">
         <v>180</v>
       </c>
-      <c r="E57" t="s">
-        <v>181</v>
+      <c r="E57" s="5" t="s">
+        <v>321</v>
       </c>
       <c r="F57" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
@@ -2699,7 +2703,7 @@
         <v>178</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
@@ -2707,19 +2711,19 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C59" t="s">
         <v>39</v>
       </c>
       <c r="D59" t="s">
+        <v>201</v>
+      </c>
+      <c r="E59" t="s">
         <v>202</v>
       </c>
-      <c r="E59" t="s">
-        <v>203</v>
-      </c>
       <c r="F59" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
@@ -2727,19 +2731,19 @@
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>185</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
@@ -2753,13 +2757,13 @@
         <v>7</v>
       </c>
       <c r="D61" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E61" t="s">
         <v>116</v>
       </c>
       <c r="F61" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
@@ -2779,7 +2783,7 @@
         <v>114</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
@@ -2799,7 +2803,7 @@
         <v>154</v>
       </c>
       <c r="F63" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
@@ -2819,7 +2823,7 @@
         <v>61</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
@@ -2827,16 +2831,16 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C65" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D65" t="s">
         <v>24</v>
       </c>
       <c r="F65" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
@@ -2844,17 +2848,17 @@
         <v>65</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
@@ -2862,7 +2866,7 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C67" t="s">
         <v>16</v>
@@ -2871,7 +2875,7 @@
         <v>24</v>
       </c>
       <c r="F67" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
@@ -2879,17 +2883,17 @@
         <v>67</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
@@ -2897,7 +2901,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C69" t="s">
         <v>16</v>
@@ -2906,7 +2910,7 @@
         <v>24</v>
       </c>
       <c r="F69" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
@@ -2917,7 +2921,7 @@
         <v>146</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>147</v>
@@ -2926,7 +2930,7 @@
         <v>148</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
@@ -2946,7 +2950,7 @@
         <v>156</v>
       </c>
       <c r="F71" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
@@ -2954,7 +2958,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>14</v>
@@ -2963,10 +2967,10 @@
         <v>36</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
@@ -2974,19 +2978,19 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
+        <v>206</v>
+      </c>
+      <c r="C73" t="s">
+        <v>289</v>
+      </c>
+      <c r="D73" t="s">
+        <v>319</v>
+      </c>
+      <c r="E73" t="s">
         <v>207</v>
       </c>
-      <c r="C73" t="s">
-        <v>291</v>
-      </c>
-      <c r="D73" t="s">
-        <v>321</v>
-      </c>
-      <c r="E73" t="s">
-        <v>208</v>
-      </c>
       <c r="F73" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
@@ -3000,13 +3004,13 @@
         <v>7</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>144</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
@@ -3020,13 +3024,13 @@
         <v>16</v>
       </c>
       <c r="D75" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E75" t="s">
         <v>87</v>
       </c>
       <c r="F75" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
@@ -3037,7 +3041,7 @@
         <v>94</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>18</v>
@@ -3046,7 +3050,7 @@
         <v>95</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
@@ -3066,7 +3070,7 @@
         <v>28</v>
       </c>
       <c r="F77" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
@@ -3086,7 +3090,7 @@
         <v>108</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
@@ -3094,7 +3098,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C79" t="s">
         <v>39</v>
@@ -3103,7 +3107,7 @@
         <v>71</v>
       </c>
       <c r="F79" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
@@ -3114,7 +3118,7 @@
         <v>162</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>8</v>
@@ -3123,7 +3127,7 @@
         <v>163</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
@@ -3143,7 +3147,7 @@
         <v>9</v>
       </c>
       <c r="F81" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
@@ -3163,7 +3167,7 @@
         <v>101</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
@@ -3171,16 +3175,16 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C83" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D83" t="s">
         <v>180</v>
       </c>
       <c r="F83" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
@@ -3200,7 +3204,7 @@
         <v>65</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
@@ -3211,7 +3215,7 @@
         <v>96</v>
       </c>
       <c r="C85" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D85" t="s">
         <v>90</v>
@@ -3220,7 +3224,7 @@
         <v>97</v>
       </c>
       <c r="F85" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
@@ -3240,7 +3244,7 @@
         <v>145</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
@@ -3260,7 +3264,7 @@
         <v>121</v>
       </c>
       <c r="F87" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
@@ -3280,7 +3284,7 @@
         <v>166</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
@@ -3288,7 +3292,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C89" t="s">
         <v>7</v>
@@ -3297,7 +3301,7 @@
         <v>176</v>
       </c>
       <c r="F89" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
@@ -3308,7 +3312,7 @@
         <v>45</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>34</v>
@@ -3317,7 +3321,7 @@
         <v>46</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
@@ -3337,7 +3341,7 @@
         <v>105</v>
       </c>
       <c r="F91" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
@@ -3357,7 +3361,7 @@
         <v>82</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
@@ -3377,7 +3381,7 @@
         <v>35</v>
       </c>
       <c r="F93" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
@@ -3397,7 +3401,7 @@
         <v>159</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
@@ -3417,7 +3421,7 @@
         <v>41</v>
       </c>
       <c r="F95" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
@@ -3437,7 +3441,7 @@
         <v>5</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
@@ -3448,7 +3452,7 @@
         <v>83</v>
       </c>
       <c r="C97" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D97" t="s">
         <v>84</v>
@@ -3457,7 +3461,7 @@
         <v>85</v>
       </c>
       <c r="F97" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
@@ -3465,19 +3469,19 @@
         <v>97</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D98" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E98" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="E98" s="2" t="s">
-        <v>191</v>
-      </c>
       <c r="F98" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
@@ -3485,16 +3489,16 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C99" t="s">
         <v>39</v>
       </c>
       <c r="D99" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F99" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>

--- a/kadro/ok.xlsx
+++ b/kadro/ok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kahra\OneDrive\Documents\GitHub\ulkemyanimda.github.io\kadro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ACE535B-4F1A-437A-8C15-A73F58A7D039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A03EE5B7-C20E-42E5-A3BE-1D73BD70B5B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="334">
   <si>
     <t>Ad-Soyad</t>
   </si>
@@ -347,9 +347,6 @@
     <t>Merak eden, sorgulayan, hayatın küçük keyiflerinden hoşlanan, kültürel faaliyetlere önem veren, sürekli kendini geliştiren, mesleğine değer veren ve düşünmeyi seven biriyimdir.</t>
   </si>
   <si>
-    <t>SUAT ÖZER</t>
-  </si>
-  <si>
     <t>Burdur’da Türk Dili ve Edebiyatı öğretmeni olarak çalışmaktayım. Yurtdışında BAKANLIK/Yurtdışı-Slovakya/T.C. Bratislava Büyükelçiliği Eğitim Müşavirliği bünyesinde okutman olarak yaklaşık 1 sene çalıştım. Alanımda doktora yaptım.</t>
   </si>
   <si>
@@ -419,9 +416,6 @@
   </si>
   <si>
     <t>Gaziantep</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Milli Eğitim Bakanlığı bünyesinde altı yıllık bir mesleki deneyime sahibim. Türkçenin konuşma dil becerisi alanında tezli yüksek lisansımı tamamladım. Türkçenin zengin dünyasını öğrenmeyi ve öğretmeyi kendine ilke edinmiş bir öğretmenim. </t>
   </si>
   <si>
     <t>Zehra YILMAZ</t>
@@ -798,9 +792,6 @@
 Amacım; merak eden, düşünen, keşfetmeye cesaret eden ve kendini ifade edebilen çocukların yetişmesine katkı sağlamak. Her çocuğun içinde keşfedilmeyi bekleyen bir potansiyel olduğuna inanıyor ve bu potansiyelin ortaya çıkmasına rehberlik etmeyi en değerli görevim olarak görüyorum.</t>
   </si>
   <si>
-    <t>17/05/1979 tarihinde Kırıkkale’de doğdum.İlkokul,ortaokul ve liseyi Kırıkkale’de okuduktan sonra Ankara Üniversitesi Dil ve Tarih Coğrafya Fakültesi Dil Bilim bölümünü bitirdim.Üniversitede ikinci dil olarak Japonca öğrendim.2001 yılında ilk görev yerim olan Bayburt Lisesine İngilizce öğretmeni olarak atandım.Daha sonra Kırşehir ve Burdur Gölhisar ‘da görev yaptım.Şu an Antalya Kumluca Mavikent Mustafa Ayşe Acarbulut Anadolu Lisesinde görev yapmaktayım.Erzurum’da English Together ve Mersin Hizmet İçi Eğitim Enstitüsünde CEFR seminerine katıldım.Erasmus KA2 projelerinde yer alıyorum.Başvurumuz sonrasında okulumuz Akredite bir kurum oldu.Ayrıca,Yabancılara Türkçe Öğretimi Sertifikam var.</t>
-  </si>
-  <si>
     <t>FATMA NÜKTE</t>
   </si>
   <si>
@@ -1134,6 +1125,54 @@
 Eğitim yaklaşımımı desteklemek için yaratıcı drama, eTwinning projeleri ve etkileşim odaklı yöntemlerle çalışıyorum. Ayrıca, “İğne Deliğinden Dünya” ve “Etkileşim Odaklı Disiplinlerarası Oyunlar” kitaplarının yazarlarından biriyim. Eğitsel oyunlar ve oyunlaştırma üzerine çalışmayı ve içerik geliştirmeyi özellikle seviyorum.
 Derslerimde amacım, öğrencilerin bilgiyi sorgulamalarını, kendi bakış açılarını geliştirmelerini ve öğrenmeyi aktif hâle getirmelerini sağlamak. Her öğrencinin öğrenme yolculuğunu anlamlı ve keşif odaklı hâle getirmek temel hedefim.
 Günümüzde dijital ortamların hem besleyen hem de dikkat edilmesi gereken alanlar olduğunu düşünüyorum. Bu düşüncelerimden hareketle eleştirel dijital okuryazarlık doktora araştırmama devam ediyorum.</t>
+  </si>
+  <si>
+    <t>Yeşim Oğul, Türkçe eğitimi ve dil çalışmaları alanında uzmanlaşmış, akademik ve uygulamalı deneyimi güçlü bir eğitimcidir. Karadeniz Teknik Üniversitesi Fatih Eğitim Fakültesi Türkçe Öğretmenliği lisans eğitiminin ardından, aynı üniversitenin Sosyal Bilimler Enstitüsü Türk Dili ve Edebiyatı alanında yüksek lisansını tamamlamıştır. Ayrıca Anadolu Üniversitesi Siyaset Bilimi ve Kamu Yönetimi bölümünde öğrenim görmüştür.
+2006 yılından bu yana eğitim alanında görev yapan Oğul; öğretmenlik ve yöneticilik deneyimlerinin ardından hâlen Trabzon Faruk Başaran Bilim ve Sanat Merkezi’nde görev yapmakta, eş zamanlı olarak Karadeniz Teknik Üniversitesi TÖMER bünyesinde yabancı dil olarak Türkçe öğretimi alanında öğretim görevlisi olarak çalışmaktadır.
+Akademik çalışmalarının yanı sıra sosyal sorumluluk projelerinde de aktif rol alan Oğul, Türk Kızılayı bünyesinde gönüllü afet liderliği, kamp liderliği ve çeşitli toplumsal dayanışma faaliyetlerinde yer almıştır.
+Türkçe eğitimi, dil becerileri ve öğretim yöntemleri üzerine yayımlanmış akademik çalışmaları, proje danışmanlıkları ve ulusal/uluslararası eğitim projelerindeki katkılarıyla mesleki gelişimini sürdürmektedir.</t>
+  </si>
+  <si>
+    <t>Dokuz Eylül Üniversitesi  mezunuyum.  Ülkem yanımda platformunda Türkçe ve Türk kültürü  öğretmeni  olarak görev  yapmaktan büyük mutluluk duyuyorum. Eğitimde yenilikçi uygulamalara önem veriyorum .</t>
+  </si>
+  <si>
+    <t>./img/yogul.jpg</t>
+  </si>
+  <si>
+    <t>./img/ffaki.jpg</t>
+  </si>
+  <si>
+    <t>./img/arozturk.jpg</t>
+  </si>
+  <si>
+    <t>./img/eertekin.jpg</t>
+  </si>
+  <si>
+    <t>./img/gkama.jpg</t>
+  </si>
+  <si>
+    <t>Suat ÖZER</t>
+  </si>
+  <si>
+    <t>./img/sozer.jpg</t>
+  </si>
+  <si>
+    <t>./img/ouysal.jpg</t>
+  </si>
+  <si>
+    <t>./img/hdundar.jpg</t>
+  </si>
+  <si>
+    <t>./img/myucel.jpg</t>
+  </si>
+  <si>
+    <t>./img/nakbulut.jpg</t>
+  </si>
+  <si>
+    <t>./img/eyesil.jpg</t>
+  </si>
+  <si>
+    <t>17/05/1979 tarihinde Kırıkkale’de doğdum.İlkokul,ortaokul ve liseyi Kırıkkale’de okuduktan sonra Ankara Üniversitesi Dil ve Tarih Coğrafya Fakültesi Dil Bilim bölümünü bitirdim.Üniversitede ikinci dil olarak Japonca öğrendim.2001 yılında ilk görev yerim olan Bayburt Lisesine İngilizce öğretmeni olarak atandım.Daha sonra Kırşehir ve Burdur Gölhisar ‘da görev yaptım. Şu an Antalya Kumluca Mavikent Mustafa Ayşe Acarbulut Anadolu Lisesinde başöğretmen olarak görev yapmaktayım. Erzurum’da English Together ve Mersin Hizmet İçi Eğitim Enstitüsünde CEFR seminerine katıldım.Erasmus KA2 projelerinde yer alıyorum. Başvurumuz sonrasında okulumuz Akredite bir kurum oldu. Ayrıca,Yabancılara Türkçe Öğretimi Sertifikam var.</t>
   </si>
 </sst>
 </file>
@@ -1222,7 +1261,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1230,12 +1269,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1539,7 +1572,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F99"/>
+  <dimension ref="A1:F100"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="23.33203125" bestFit="1" customWidth="1"/>
@@ -1563,10 +1596,10 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -1577,7 +1610,7 @@
         <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>30</v>
@@ -1586,7 +1619,7 @@
         <v>31</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1594,7 +1627,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C3" t="s">
         <v>23</v>
@@ -1603,10 +1636,10 @@
         <v>73</v>
       </c>
       <c r="E3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F3" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -1614,19 +1647,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>112</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1634,10 +1667,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C5" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D5" t="s">
         <v>73</v>
@@ -1646,7 +1679,7 @@
         <v>74</v>
       </c>
       <c r="F5" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -1654,7 +1687,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>7</v>
@@ -1663,10 +1696,10 @@
         <v>24</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -1674,19 +1707,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" t="s">
         <v>88</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>89</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>90</v>
       </c>
-      <c r="E7" t="s">
-        <v>91</v>
-      </c>
       <c r="F7" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -1694,19 +1727,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -1714,19 +1747,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C9" t="s">
         <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E9" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F9" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -1734,7 +1767,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>16</v>
@@ -1743,10 +1776,10 @@
         <v>24</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -1766,7 +1799,7 @@
         <v>70</v>
       </c>
       <c r="F11" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -1786,7 +1819,7 @@
         <v>52</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -1794,19 +1827,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C13" t="s">
         <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E13" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F13" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -1814,19 +1847,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -1837,7 +1870,7 @@
         <v>47</v>
       </c>
       <c r="C15" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="D15" t="s">
         <v>48</v>
@@ -1846,7 +1879,7 @@
         <v>49</v>
       </c>
       <c r="F15" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -1866,7 +1899,7 @@
         <v>15</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -1886,7 +1919,7 @@
         <v>68</v>
       </c>
       <c r="F17" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -1894,7 +1927,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>16</v>
@@ -1903,10 +1936,10 @@
         <v>36</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -1914,7 +1947,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C19" t="s">
         <v>7</v>
@@ -1923,10 +1956,10 @@
         <v>8</v>
       </c>
       <c r="E19" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F19" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -1934,19 +1967,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -1966,7 +1999,7 @@
         <v>63</v>
       </c>
       <c r="F21" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -1986,7 +2019,7 @@
         <v>19</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -1994,7 +2027,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C23" t="s">
         <v>39</v>
@@ -2003,10 +2036,10 @@
         <v>73</v>
       </c>
       <c r="E23" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F23" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -2014,7 +2047,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>39</v>
@@ -2023,10 +2056,10 @@
         <v>24</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -2034,7 +2067,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C25" t="s">
         <v>7</v>
@@ -2043,10 +2076,10 @@
         <v>48</v>
       </c>
       <c r="E25" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F25" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -2054,19 +2087,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -2074,7 +2107,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C27" t="s">
         <v>23</v>
@@ -2083,10 +2116,10 @@
         <v>34</v>
       </c>
       <c r="E27" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F27" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -2106,7 +2139,7 @@
         <v>54</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -2114,19 +2147,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C29" t="s">
         <v>14</v>
       </c>
       <c r="D29" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E29" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F29" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -2134,7 +2167,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>14</v>
@@ -2143,10 +2176,10 @@
         <v>34</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -2154,19 +2187,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C31" t="s">
         <v>7</v>
       </c>
       <c r="D31" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E31" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F31" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
@@ -2174,7 +2207,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>7</v>
@@ -2183,10 +2216,10 @@
         <v>11</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
@@ -2206,7 +2239,7 @@
         <v>12</v>
       </c>
       <c r="F33" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -2214,7 +2247,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>23</v>
@@ -2223,10 +2256,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -2246,7 +2279,7 @@
         <v>80</v>
       </c>
       <c r="F35" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -2254,7 +2287,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>14</v>
@@ -2263,10 +2296,10 @@
         <v>34</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -2274,39 +2307,39 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C37" t="s">
         <v>23</v>
       </c>
       <c r="D37" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E37" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F37" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="409.6" x14ac:dyDescent="0.3">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>320</v>
+        <v>216</v>
+      </c>
+      <c r="E38" t="s">
+        <v>317</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -2314,19 +2347,19 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C39" t="s">
         <v>14</v>
       </c>
       <c r="D39" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E39" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F39" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -2334,7 +2367,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>7</v>
@@ -2343,10 +2376,10 @@
         <v>79</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -2366,7 +2399,7 @@
         <v>25</v>
       </c>
       <c r="F41" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -2374,7 +2407,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>39</v>
@@ -2383,10 +2416,10 @@
         <v>8</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -2406,7 +2439,7 @@
         <v>43</v>
       </c>
       <c r="F43" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -2414,7 +2447,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>14</v>
@@ -2423,10 +2456,10 @@
         <v>24</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -2440,13 +2473,13 @@
         <v>14</v>
       </c>
       <c r="D45" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="E45" t="s">
         <v>21</v>
       </c>
       <c r="F45" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -2457,7 +2490,7 @@
         <v>55</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>56</v>
@@ -2466,7 +2499,7 @@
         <v>57</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -2474,10 +2507,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C47" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D47" t="s">
         <v>71</v>
@@ -2486,7 +2519,7 @@
         <v>72</v>
       </c>
       <c r="F47" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -2494,19 +2527,19 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
@@ -2514,19 +2547,19 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
+        <v>201</v>
+      </c>
+      <c r="C49" t="s">
+        <v>285</v>
+      </c>
+      <c r="D49" t="s">
+        <v>202</v>
+      </c>
+      <c r="E49" t="s">
         <v>203</v>
       </c>
-      <c r="C49" t="s">
-        <v>288</v>
-      </c>
-      <c r="D49" t="s">
-        <v>204</v>
-      </c>
-      <c r="E49" t="s">
-        <v>205</v>
-      </c>
       <c r="F49" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -2534,7 +2567,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>7</v>
@@ -2546,7 +2579,7 @@
         <v>37</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
@@ -2554,16 +2587,16 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C51" t="s">
         <v>16</v>
       </c>
       <c r="D51" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F51" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
@@ -2571,19 +2604,19 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
@@ -2594,16 +2627,16 @@
         <v>58</v>
       </c>
       <c r="C53" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D53" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="E53" t="s">
         <v>59</v>
       </c>
       <c r="F53" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
@@ -2611,19 +2644,19 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
@@ -2643,7 +2676,7 @@
         <v>77</v>
       </c>
       <c r="F55" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
@@ -2651,39 +2684,39 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="409.6" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C57" t="s">
         <v>23</v>
       </c>
       <c r="D57" t="s">
-        <v>180</v>
-      </c>
-      <c r="E57" s="5" t="s">
-        <v>321</v>
+        <v>178</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>318</v>
       </c>
       <c r="F57" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
@@ -2691,19 +2724,19 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D58" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E58" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="E58" s="2" t="s">
-        <v>178</v>
-      </c>
       <c r="F58" s="2" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
@@ -2711,19 +2744,19 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C59" t="s">
         <v>39</v>
       </c>
       <c r="D59" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E59" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F59" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
@@ -2731,19 +2764,19 @@
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
@@ -2751,19 +2784,19 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C61" t="s">
         <v>7</v>
       </c>
       <c r="D61" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="E61" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F61" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
@@ -2771,19 +2804,19 @@
         <v>61</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
@@ -2791,719 +2824,740 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C63" t="s">
         <v>7</v>
       </c>
       <c r="D63" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E63" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F63" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="2">
+      <c r="A64">
         <v>63</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C64" s="2" t="s">
+      <c r="B64" t="s">
+        <v>301</v>
+      </c>
+      <c r="C64" t="s">
         <v>16</v>
       </c>
-      <c r="D64" s="2" t="s">
+      <c r="D64" t="s">
         <v>24</v>
       </c>
-      <c r="E64" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>285</v>
+      <c r="F64" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65">
+        <v>63</v>
+      </c>
+      <c r="B65" t="s">
+        <v>326</v>
+      </c>
+      <c r="C65" t="s">
+        <v>16</v>
+      </c>
+      <c r="D65" t="s">
+        <v>314</v>
+      </c>
+      <c r="E65" t="s">
+        <v>86</v>
+      </c>
+      <c r="F65" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>63</v>
+      </c>
+      <c r="B66" t="s">
+        <v>298</v>
+      </c>
+      <c r="C66" t="s">
+        <v>39</v>
+      </c>
+      <c r="D66" t="s">
+        <v>71</v>
+      </c>
+      <c r="F66" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A67" s="2">
+        <v>63</v>
+      </c>
+      <c r="B67" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B65" t="s">
-        <v>298</v>
-      </c>
-      <c r="C65" t="s">
-        <v>306</v>
-      </c>
-      <c r="D65" t="s">
-        <v>24</v>
-      </c>
-      <c r="F65" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="2">
+      <c r="C67" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E67" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B66" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E66" s="2"/>
-      <c r="F66" s="2" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67">
-        <v>66</v>
-      </c>
-      <c r="B67" t="s">
-        <v>302</v>
-      </c>
-      <c r="C67" t="s">
-        <v>16</v>
-      </c>
-      <c r="D67" t="s">
-        <v>24</v>
-      </c>
-      <c r="F67" t="s">
-        <v>285</v>
+      <c r="F67" s="2" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>303</v>
+        <v>162</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>309</v>
+        <v>7</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E68" s="2"/>
+        <v>163</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>164</v>
+      </c>
       <c r="F68" s="2" t="s">
-        <v>285</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B69" t="s">
-        <v>304</v>
+        <v>103</v>
       </c>
       <c r="C69" t="s">
         <v>16</v>
       </c>
       <c r="D69" t="s">
-        <v>24</v>
+        <v>34</v>
+      </c>
+      <c r="E69" t="s">
+        <v>104</v>
       </c>
       <c r="F69" t="s">
-        <v>285</v>
+        <v>329</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>294</v>
+        <v>7</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>285</v>
+        <v>323</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B71" t="s">
-        <v>155</v>
+        <v>26</v>
       </c>
       <c r="C71" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="D71" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E71" t="s">
-        <v>156</v>
+        <v>28</v>
       </c>
       <c r="F71" t="s">
-        <v>285</v>
+        <v>332</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="2">
-        <v>71</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>285</v>
+      <c r="A72">
+        <v>63</v>
+      </c>
+      <c r="B72" t="s">
+        <v>302</v>
+      </c>
+      <c r="C72" t="s">
+        <v>23</v>
+      </c>
+      <c r="D72" t="s">
+        <v>307</v>
+      </c>
+      <c r="E72" t="s">
+        <v>319</v>
+      </c>
+      <c r="F72" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73">
-        <v>72</v>
-      </c>
-      <c r="B73" t="s">
-        <v>206</v>
-      </c>
-      <c r="C73" t="s">
-        <v>289</v>
-      </c>
-      <c r="D73" t="s">
-        <v>319</v>
-      </c>
-      <c r="E73" t="s">
-        <v>207</v>
-      </c>
-      <c r="F73" t="s">
-        <v>285</v>
+      <c r="A73" s="2">
+        <v>63</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
-        <v>73</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>285</v>
+        <v>64</v>
+      </c>
+      <c r="B74" t="s">
+        <v>44</v>
+      </c>
+      <c r="C74" t="s">
+        <v>23</v>
+      </c>
+      <c r="D74" t="s">
+        <v>89</v>
+      </c>
+      <c r="E74" t="s">
+        <v>320</v>
+      </c>
+      <c r="F74" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B75" t="s">
-        <v>86</v>
+        <v>295</v>
       </c>
       <c r="C75" t="s">
-        <v>16</v>
+        <v>303</v>
       </c>
       <c r="D75" t="s">
-        <v>317</v>
-      </c>
-      <c r="E75" t="s">
-        <v>87</v>
+        <v>24</v>
       </c>
       <c r="F75" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>94</v>
+        <v>296</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>95</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="E76" s="2"/>
       <c r="F76" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B77" t="s">
-        <v>26</v>
+        <v>299</v>
       </c>
       <c r="C77" t="s">
         <v>16</v>
       </c>
       <c r="D77" t="s">
-        <v>27</v>
-      </c>
-      <c r="E77" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F77" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>106</v>
+        <v>300</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>23</v>
+        <v>306</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>108</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="E78" s="2"/>
       <c r="F78" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B79" t="s">
-        <v>301</v>
+        <v>153</v>
       </c>
       <c r="C79" t="s">
         <v>39</v>
       </c>
       <c r="D79" t="s">
-        <v>71</v>
+        <v>30</v>
+      </c>
+      <c r="E79" t="s">
+        <v>154</v>
       </c>
       <c r="F79" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>162</v>
+        <v>206</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>288</v>
+        <v>14</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>163</v>
+        <v>333</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B81" t="s">
-        <v>6</v>
+        <v>204</v>
       </c>
       <c r="C81" t="s">
-        <v>7</v>
+        <v>286</v>
       </c>
       <c r="D81" t="s">
-        <v>8</v>
+        <v>316</v>
       </c>
       <c r="E81" t="s">
-        <v>9</v>
+        <v>205</v>
       </c>
       <c r="F81" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>100</v>
+        <v>141</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>73</v>
+        <v>315</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83">
-        <v>82</v>
-      </c>
-      <c r="B83" t="s">
-        <v>300</v>
-      </c>
-      <c r="C83" t="s">
-        <v>308</v>
-      </c>
-      <c r="D83" t="s">
-        <v>180</v>
-      </c>
-      <c r="F83" t="s">
-        <v>285</v>
+      <c r="A83" s="2">
+        <v>75</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>65</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="E84" s="2"/>
       <c r="F84" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85" s="2">
+        <v>79</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C85" s="2" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85">
-        <v>84</v>
-      </c>
-      <c r="B85" t="s">
-        <v>96</v>
-      </c>
-      <c r="C85" t="s">
-        <v>288</v>
-      </c>
-      <c r="D85" t="s">
-        <v>90</v>
-      </c>
-      <c r="E85" t="s">
-        <v>97</v>
-      </c>
-      <c r="F85" t="s">
-        <v>285</v>
+      <c r="D85" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>145</v>
+        <v>61</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B87" t="s">
-        <v>119</v>
+        <v>6</v>
       </c>
       <c r="C87" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="D87" t="s">
-        <v>120</v>
+        <v>8</v>
       </c>
       <c r="E87" t="s">
-        <v>121</v>
+        <v>9</v>
       </c>
       <c r="F87" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>164</v>
+        <v>99</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>166</v>
+        <v>100</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B89" t="s">
         <v>297</v>
       </c>
       <c r="C89" t="s">
-        <v>7</v>
+        <v>305</v>
       </c>
       <c r="D89" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F89" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <v>84</v>
+      </c>
+      <c r="B90" t="s">
+        <v>95</v>
+      </c>
+      <c r="C90" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="2">
+      <c r="D90" t="s">
         <v>89</v>
       </c>
-      <c r="B90" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>285</v>
+      <c r="E90" t="s">
+        <v>96</v>
+      </c>
+      <c r="F90" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91">
-        <v>90</v>
-      </c>
-      <c r="B91" t="s">
-        <v>104</v>
-      </c>
-      <c r="C91" t="s">
-        <v>16</v>
-      </c>
-      <c r="D91" t="s">
-        <v>34</v>
-      </c>
-      <c r="E91" t="s">
-        <v>105</v>
-      </c>
-      <c r="F91" t="s">
-        <v>285</v>
+      <c r="A91" s="2">
+        <v>85</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="2">
-        <v>91</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>285</v>
+      <c r="A92">
+        <v>86</v>
+      </c>
+      <c r="B92" t="s">
+        <v>117</v>
+      </c>
+      <c r="C92" t="s">
+        <v>39</v>
+      </c>
+      <c r="D92" t="s">
+        <v>118</v>
+      </c>
+      <c r="E92" t="s">
+        <v>119</v>
+      </c>
+      <c r="F92" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B93" t="s">
-        <v>32</v>
+        <v>294</v>
       </c>
       <c r="C93" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="D93" t="s">
-        <v>34</v>
-      </c>
-      <c r="E93" t="s">
-        <v>35</v>
+        <v>174</v>
       </c>
       <c r="F93" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>157</v>
+        <v>45</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>7</v>
+        <v>288</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>158</v>
+        <v>34</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>159</v>
+        <v>46</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95">
-        <v>94</v>
-      </c>
-      <c r="B95" t="s">
-        <v>38</v>
-      </c>
-      <c r="C95" t="s">
-        <v>39</v>
-      </c>
-      <c r="D95" t="s">
-        <v>40</v>
-      </c>
-      <c r="E95" t="s">
-        <v>41</v>
-      </c>
-      <c r="F95" t="s">
-        <v>285</v>
+      <c r="A95" s="2">
+        <v>91</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="2">
-        <v>95</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F96" s="2" t="s">
-        <v>285</v>
+      <c r="A96">
+        <v>92</v>
+      </c>
+      <c r="B96" t="s">
+        <v>32</v>
+      </c>
+      <c r="C96" t="s">
+        <v>33</v>
+      </c>
+      <c r="D96" t="s">
+        <v>34</v>
+      </c>
+      <c r="E96" t="s">
+        <v>35</v>
+      </c>
+      <c r="F96" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B97" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="C97" t="s">
-        <v>294</v>
+        <v>39</v>
       </c>
       <c r="D97" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="E97" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="F97" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>188</v>
+        <v>3</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>189</v>
+        <v>4</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>190</v>
+        <v>5</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B99" t="s">
-        <v>305</v>
+        <v>83</v>
       </c>
       <c r="C99" t="s">
-        <v>39</v>
+        <v>291</v>
       </c>
       <c r="D99" t="s">
-        <v>310</v>
+        <v>84</v>
+      </c>
+      <c r="E99" t="s">
+        <v>85</v>
       </c>
       <c r="F99" t="s">
-        <v>285</v>
+        <v>282</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100" s="2">
+        <v>97</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>282</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:F101">
-    <sortCondition descending="1" ref="B1:B101"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F100">
+    <sortCondition ref="A54:A100"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/kadro/ok.xlsx
+++ b/kadro/ok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kahra\OneDrive\Documents\GitHub\ulkemyanimda.github.io\kadro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A03EE5B7-C20E-42E5-A3BE-1D73BD70B5B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C58D0AB9-FB5D-4999-A62A-4D41E45EB450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="336">
   <si>
     <t>Ad-Soyad</t>
   </si>
@@ -1173,6 +1173,12 @@
   </si>
   <si>
     <t>17/05/1979 tarihinde Kırıkkale’de doğdum.İlkokul,ortaokul ve liseyi Kırıkkale’de okuduktan sonra Ankara Üniversitesi Dil ve Tarih Coğrafya Fakültesi Dil Bilim bölümünü bitirdim.Üniversitede ikinci dil olarak Japonca öğrendim.2001 yılında ilk görev yerim olan Bayburt Lisesine İngilizce öğretmeni olarak atandım.Daha sonra Kırşehir ve Burdur Gölhisar ‘da görev yaptım. Şu an Antalya Kumluca Mavikent Mustafa Ayşe Acarbulut Anadolu Lisesinde başöğretmen olarak görev yapmaktayım. Erzurum’da English Together ve Mersin Hizmet İçi Eğitim Enstitüsünde CEFR seminerine katıldım.Erasmus KA2 projelerinde yer alıyorum. Başvurumuz sonrasında okulumuz Akredite bir kurum oldu. Ayrıca,Yabancılara Türkçe Öğretimi Sertifikam var.</t>
+  </si>
+  <si>
+    <t>1997 yılında Gümüşhane’de doğdum. 2020 yılında Karadeniz Teknik Üniversitesi Türkçe Öğretmenliği bölümünden mezun oldum. Üniversite yıllarımda Çağdaş Drama Derneğinde 5 aşamalı yaratıcı drama eğitimi alıp bitirdim. Çeşitli ses, ritim atölyelerine katıldım. Şimdi ise yine Trabzon Üniversitesi Okul Öncesi Öğretmenliği bölümüne devam etmekteyim. Erzincan Binali Yıldırım Üniversitesi Türkçe Sosyal Bilimler Enstitüsü/ Türkçe Eğitimi alanında yüksek lisans yapmaktayım. 2023 yılından beri Gümüşhane’de Türkçe öğretmeni olarak çalışmaktayım. Ülkem Yanımda platformunda da Hollanda ve İskandinav ülkelerindeki Türk çocuklarına Türkçe ve Türk Kültürü dersi vermekteyim. Bu dersler aracılığıyla amacım, dünyanın neresinde olursa olsun Türk dilini ve Türk Kültürünü öğreterek kültürel mirasımızı kaybetmeden gelecek nesillere aktarmaktır. Bu platformdaki deneyim ve tecrübelerle birlikte uluslararası düzeyde bilgilerimi aktarmaya devam edip çeşitli çalışmalarda bulunmayı amaçlıyorum.</t>
+  </si>
+  <si>
+    <t>./img/akansu.jpg</t>
   </si>
 </sst>
 </file>
@@ -2889,6 +2895,9 @@
       <c r="D66" t="s">
         <v>71</v>
       </c>
+      <c r="E66" t="s">
+        <v>334</v>
+      </c>
       <c r="F66" t="s">
         <v>330</v>
       </c>
@@ -3034,190 +3043,187 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="2">
+      <c r="A74">
+        <v>63</v>
+      </c>
+      <c r="B74" t="s">
+        <v>294</v>
+      </c>
+      <c r="C74" t="s">
+        <v>7</v>
+      </c>
+      <c r="D74" t="s">
+        <v>174</v>
+      </c>
+      <c r="F74" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A75" s="2">
         <v>64</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B75" t="s">
         <v>44</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C75" t="s">
         <v>23</v>
       </c>
-      <c r="D74" t="s">
+      <c r="D75" t="s">
         <v>89</v>
       </c>
-      <c r="E74" t="s">
+      <c r="E75" t="s">
         <v>320</v>
       </c>
-      <c r="F74" t="s">
+      <c r="F75" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76">
         <v>64</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B76" t="s">
         <v>295</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C76" t="s">
         <v>303</v>
       </c>
-      <c r="D75" t="s">
+      <c r="D76" t="s">
         <v>24</v>
       </c>
-      <c r="F75" t="s">
+      <c r="F76" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="2">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A77" s="2">
         <v>65</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="B77" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="C77" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="D76" s="2" t="s">
+      <c r="D77" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E76" s="2"/>
-      <c r="F76" s="2" t="s">
+      <c r="E77" s="2"/>
+      <c r="F77" s="2" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78">
         <v>66</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B78" t="s">
         <v>299</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C78" t="s">
         <v>16</v>
       </c>
-      <c r="D77" t="s">
+      <c r="D78" t="s">
         <v>24</v>
       </c>
-      <c r="F77" t="s">
+      <c r="F78" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="2">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79" s="2">
         <v>67</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="B79" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C79" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="D78" s="2" t="s">
+      <c r="D79" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E78" s="2"/>
-      <c r="F78" s="2" t="s">
+      <c r="E79" s="2"/>
+      <c r="F79" s="2" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A80">
         <v>70</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B80" t="s">
         <v>153</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C80" t="s">
         <v>39</v>
       </c>
-      <c r="D79" t="s">
+      <c r="D80" t="s">
         <v>30</v>
       </c>
-      <c r="E79" t="s">
+      <c r="E80" t="s">
         <v>154</v>
       </c>
-      <c r="F79" t="s">
+      <c r="F80" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="2">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81" s="2">
         <v>71</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="B81" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="C81" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D80" s="2" t="s">
+      <c r="D81" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E80" s="2" t="s">
+      <c r="E81" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="F80" s="2" t="s">
+      <c r="F81" s="2" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82">
         <v>72</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B82" t="s">
         <v>204</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C82" t="s">
         <v>286</v>
       </c>
-      <c r="D81" t="s">
+      <c r="D82" t="s">
         <v>316</v>
       </c>
-      <c r="E81" t="s">
+      <c r="E82" t="s">
         <v>205</v>
       </c>
-      <c r="F81" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="2">
-        <v>73</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F82" s="2" t="s">
+      <c r="F82" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>93</v>
+        <v>141</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>291</v>
+        <v>7</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>18</v>
+        <v>315</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>94</v>
+        <v>142</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>282</v>
@@ -3225,191 +3231,194 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>23</v>
+        <v>291</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="E84" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>94</v>
+      </c>
       <c r="F84" s="2" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>160</v>
+        <v>105</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>285</v>
+        <v>23</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>161</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="E85" s="2"/>
       <c r="F85" s="2" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>16</v>
+        <v>285</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>61</v>
+        <v>161</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87">
+      <c r="A87" s="2">
         <v>80</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <v>80</v>
+      </c>
+      <c r="B88" t="s">
         <v>6</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C88" t="s">
         <v>7</v>
       </c>
-      <c r="D87" t="s">
+      <c r="D88" t="s">
         <v>8</v>
       </c>
-      <c r="E87" t="s">
+      <c r="E88" t="s">
         <v>9</v>
       </c>
-      <c r="F87" t="s">
+      <c r="F88" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="2">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89" s="2">
         <v>81</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="B89" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="C89" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D88" s="2" t="s">
+      <c r="D89" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E88" s="2" t="s">
+      <c r="E89" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F88" s="2" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89">
-        <v>82</v>
-      </c>
-      <c r="B89" t="s">
-        <v>297</v>
-      </c>
-      <c r="C89" t="s">
-        <v>305</v>
-      </c>
-      <c r="D89" t="s">
-        <v>178</v>
-      </c>
-      <c r="F89" t="s">
+      <c r="F89" s="2" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B90" t="s">
-        <v>95</v>
+        <v>297</v>
       </c>
       <c r="C90" t="s">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="D90" t="s">
-        <v>89</v>
-      </c>
-      <c r="E90" t="s">
-        <v>96</v>
+        <v>178</v>
       </c>
       <c r="F90" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="2">
+      <c r="A91">
+        <v>84</v>
+      </c>
+      <c r="B91" t="s">
+        <v>95</v>
+      </c>
+      <c r="C91" t="s">
+        <v>285</v>
+      </c>
+      <c r="D91" t="s">
+        <v>89</v>
+      </c>
+      <c r="E91" t="s">
+        <v>96</v>
+      </c>
+      <c r="F91" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A92" s="2">
         <v>85</v>
       </c>
-      <c r="B91" s="2" t="s">
+      <c r="B92" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C91" s="2" t="s">
+      <c r="C92" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D91" s="2" t="s">
+      <c r="D92" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="E91" s="2" t="s">
+      <c r="E92" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="F91" s="2" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92">
-        <v>86</v>
-      </c>
-      <c r="B92" t="s">
-        <v>117</v>
-      </c>
-      <c r="C92" t="s">
-        <v>39</v>
-      </c>
-      <c r="D92" t="s">
-        <v>118</v>
-      </c>
-      <c r="E92" t="s">
-        <v>119</v>
-      </c>
-      <c r="F92" t="s">
+      <c r="F92" s="2" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B93" t="s">
-        <v>294</v>
+        <v>117</v>
       </c>
       <c r="C93" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="D93" t="s">
-        <v>174</v>
+        <v>118</v>
+      </c>
+      <c r="E93" t="s">
+        <v>119</v>
       </c>
       <c r="F93" t="s">
         <v>282</v>
@@ -3557,7 +3566,7 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F100">
-    <sortCondition ref="A54:A100"/>
+    <sortCondition ref="A85:A100"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/kadro/ok.xlsx
+++ b/kadro/ok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kahra\OneDrive\Documents\GitHub\ulkemyanimda.github.io\kadro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C58D0AB9-FB5D-4999-A62A-4D41E45EB450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D80147D1-5AF4-4D3D-8414-BF6799956367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="337">
   <si>
     <t>Ad-Soyad</t>
   </si>
@@ -546,12 +546,6 @@
 </t>
   </si>
   <si>
-    <t>Dokuz Eylül  Üniversitesi  Sınıf  Öğretmenliği  mezunuyum. İzmir Emirsultan Ortaokulu Türkçe öğretmeniyim(Yan alan). A2 Seviyesi İngilizce biliyorum. 
-Sertifikalarım : 1-(Meb)CEFR  Yabancı Dil olarak Türkçe'nin Öğretimi Sınıf İçi Uygulamaları (30 saat). 2-(Meb )Yabancılara  Türkçe  Öğretimi  (40 saat). 3-Kayseri Üniversitesi DİLMER Yabancılara  Türkçe  Öğretimi  Eğiticinin  Eğitimi  (55 saat).    4- Yenilikçi  Yaklaşımlar  ve Türkçe Teknoloji Kullanımı(25 saat).  5-Zeka Oyunları  Eğiticinin  Eğitimi  ( Halk Eğt 30 saat)  6-(Meb) Zeka Oyunları- 1 Sertifikası  (30 saat). 7-Kapsayıcı Eğitim ve Sosyal  Uyum kursu (30 saat) . 8- Ögretmenlik Uygulaması Danışmanlığı  Eğitimi  Kursu   (24  saat) .  9-Diksiyon ve Güzel  Konuşma Eğitimi (Başkent iletişim 30 saat). 10- Diksiyon  Eğitimi  (Halk Egt  ve Meb 30 saat). 11- Geleneksel  Hamur  İşleri  Eğitimi( 30 saat). 12- Atık kağtları  değerlendirme  kursu ( sepet  örme vb).
-Yaptığım Etkinlikler: 1- Ortaokula kadar okumayı öğrenemeyen öğrencilere destek eğitimi saatinde ve boş derslerimde kendi geliştirdiğim yöntemle kısa sürede anlamlı, hızlı okumayı ve yazmayı öğretiyorum . 2-Zeka oyunlarıyla stratejik düşünme becerisi 3- Küçük  Eller Projesi ile öğrencilerime kendi kitaplarını yazdırıyorum.
- 4- Atık kağtları örgü tekniğiyle geri dönüştürüyorum (sepet vb.) . 5- Geleneksel  Hamur İşleri  6- Amatör Keman çalıyorum.</t>
-  </si>
-  <si>
     <t>Gülsen Kama</t>
   </si>
   <si>
@@ -1179,6 +1173,12 @@
   </si>
   <si>
     <t>./img/akansu.jpg</t>
+  </si>
+  <si>
+    <t>./img/eacar.jpg</t>
+  </si>
+  <si>
+    <t>./img/cayhan.jpg</t>
   </si>
 </sst>
 </file>
@@ -1578,7 +1578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F100"/>
+  <dimension ref="A1:F99"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="23.33203125" bestFit="1" customWidth="1"/>
@@ -1602,10 +1602,10 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -1616,7 +1616,7 @@
         <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>30</v>
@@ -1625,7 +1625,7 @@
         <v>31</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1645,7 +1645,7 @@
         <v>124</v>
       </c>
       <c r="F3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -1665,7 +1665,7 @@
         <v>110</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1673,10 +1673,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D5" t="s">
         <v>73</v>
@@ -1685,7 +1685,7 @@
         <v>74</v>
       </c>
       <c r="F5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -1705,7 +1705,7 @@
         <v>116</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -1725,7 +1725,7 @@
         <v>90</v>
       </c>
       <c r="F7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -1733,19 +1733,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>159</v>
-      </c>
       <c r="F8" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -1753,7 +1753,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C9" t="s">
         <v>23</v>
@@ -1762,10 +1762,10 @@
         <v>89</v>
       </c>
       <c r="E9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -1773,7 +1773,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>16</v>
@@ -1782,10 +1782,10 @@
         <v>24</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -1805,7 +1805,7 @@
         <v>70</v>
       </c>
       <c r="F11" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -1825,7 +1825,7 @@
         <v>52</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -1845,7 +1845,7 @@
         <v>136</v>
       </c>
       <c r="F13" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -1853,19 +1853,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -1876,7 +1876,7 @@
         <v>47</v>
       </c>
       <c r="C15" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D15" t="s">
         <v>48</v>
@@ -1885,7 +1885,7 @@
         <v>49</v>
       </c>
       <c r="F15" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -1905,7 +1905,7 @@
         <v>15</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -1925,7 +1925,7 @@
         <v>68</v>
       </c>
       <c r="F17" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -1945,7 +1945,7 @@
         <v>92</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -1965,7 +1965,7 @@
         <v>140</v>
       </c>
       <c r="F19" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -1985,7 +1985,7 @@
         <v>122</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -2005,7 +2005,7 @@
         <v>63</v>
       </c>
       <c r="F21" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -2025,7 +2025,7 @@
         <v>19</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -2033,7 +2033,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C23" t="s">
         <v>39</v>
@@ -2042,10 +2042,10 @@
         <v>73</v>
       </c>
       <c r="E23" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -2065,7 +2065,7 @@
         <v>102</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -2085,7 +2085,7 @@
         <v>138</v>
       </c>
       <c r="F25" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -2096,7 +2096,7 @@
         <v>97</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>24</v>
@@ -2105,7 +2105,7 @@
         <v>98</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -2113,7 +2113,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C27" t="s">
         <v>23</v>
@@ -2122,10 +2122,10 @@
         <v>34</v>
       </c>
       <c r="E27" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F27" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -2145,7 +2145,7 @@
         <v>54</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -2153,19 +2153,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C29" t="s">
         <v>14</v>
       </c>
       <c r="D29" t="s">
+        <v>171</v>
+      </c>
+      <c r="E29" t="s">
         <v>172</v>
       </c>
-      <c r="E29" t="s">
-        <v>173</v>
-      </c>
       <c r="F29" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -2173,7 +2173,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>14</v>
@@ -2182,10 +2182,10 @@
         <v>34</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -2193,19 +2193,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C31" t="s">
         <v>7</v>
       </c>
       <c r="D31" t="s">
+        <v>147</v>
+      </c>
+      <c r="E31" t="s">
         <v>148</v>
       </c>
-      <c r="E31" t="s">
-        <v>149</v>
-      </c>
       <c r="F31" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
@@ -2225,7 +2225,7 @@
         <v>129</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
@@ -2245,7 +2245,7 @@
         <v>12</v>
       </c>
       <c r="F33" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -2253,7 +2253,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>23</v>
@@ -2262,10 +2262,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -2285,7 +2285,7 @@
         <v>80</v>
       </c>
       <c r="F35" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -2293,7 +2293,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>14</v>
@@ -2302,10 +2302,10 @@
         <v>34</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -2325,7 +2325,7 @@
         <v>127</v>
       </c>
       <c r="F37" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -2333,19 +2333,19 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E38" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -2353,19 +2353,19 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C39" t="s">
         <v>14</v>
       </c>
       <c r="D39" t="s">
+        <v>191</v>
+      </c>
+      <c r="E39" t="s">
         <v>192</v>
       </c>
-      <c r="E39" t="s">
-        <v>193</v>
-      </c>
       <c r="F39" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -2373,7 +2373,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>7</v>
@@ -2382,10 +2382,10 @@
         <v>79</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -2405,7 +2405,7 @@
         <v>25</v>
       </c>
       <c r="F41" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -2425,7 +2425,7 @@
         <v>131</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -2445,7 +2445,7 @@
         <v>43</v>
       </c>
       <c r="F43" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -2453,7 +2453,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>14</v>
@@ -2462,10 +2462,10 @@
         <v>24</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -2479,13 +2479,13 @@
         <v>14</v>
       </c>
       <c r="D45" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E45" t="s">
         <v>21</v>
       </c>
       <c r="F45" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -2496,7 +2496,7 @@
         <v>55</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>56</v>
@@ -2505,7 +2505,7 @@
         <v>57</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -2513,10 +2513,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C47" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D47" t="s">
         <v>71</v>
@@ -2525,7 +2525,7 @@
         <v>72</v>
       </c>
       <c r="F47" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -2533,7 +2533,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>7</v>
@@ -2542,10 +2542,10 @@
         <v>106</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
@@ -2553,19 +2553,19 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
+        <v>200</v>
+      </c>
+      <c r="C49" t="s">
+        <v>284</v>
+      </c>
+      <c r="D49" t="s">
         <v>201</v>
       </c>
-      <c r="C49" t="s">
-        <v>285</v>
-      </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
         <v>202</v>
       </c>
-      <c r="E49" t="s">
-        <v>203</v>
-      </c>
       <c r="F49" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -2573,7 +2573,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>7</v>
@@ -2585,7 +2585,7 @@
         <v>37</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
@@ -2593,16 +2593,16 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C51" t="s">
         <v>16</v>
       </c>
       <c r="D51" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F51" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
@@ -2616,13 +2616,13 @@
         <v>7</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>133</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
@@ -2633,16 +2633,16 @@
         <v>58</v>
       </c>
       <c r="C53" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D53" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E53" t="s">
         <v>59</v>
       </c>
       <c r="F53" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
@@ -2650,19 +2650,19 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>89</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
@@ -2682,7 +2682,7 @@
         <v>77</v>
       </c>
       <c r="F55" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
@@ -2690,19 +2690,19 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E56" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="C56" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>210</v>
-      </c>
       <c r="F56" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
@@ -2710,19 +2710,19 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C57" t="s">
         <v>23</v>
       </c>
       <c r="D57" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F57" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
@@ -2730,19 +2730,19 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
@@ -2750,19 +2750,19 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C59" t="s">
         <v>39</v>
       </c>
       <c r="D59" t="s">
+        <v>198</v>
+      </c>
+      <c r="E59" t="s">
         <v>199</v>
       </c>
-      <c r="E59" t="s">
-        <v>200</v>
-      </c>
       <c r="F59" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
@@ -2770,19 +2770,19 @@
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>182</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
@@ -2796,13 +2796,13 @@
         <v>7</v>
       </c>
       <c r="D61" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E61" t="s">
         <v>114</v>
       </c>
       <c r="F61" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
@@ -2816,13 +2816,13 @@
         <v>14</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>112</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
@@ -2830,19 +2830,19 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C63" t="s">
         <v>7</v>
       </c>
       <c r="D63" t="s">
+        <v>150</v>
+      </c>
+      <c r="E63" t="s">
         <v>151</v>
       </c>
-      <c r="E63" t="s">
-        <v>152</v>
-      </c>
       <c r="F63" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
@@ -2850,7 +2850,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C64" t="s">
         <v>16</v>
@@ -2859,7 +2859,7 @@
         <v>24</v>
       </c>
       <c r="F64" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
@@ -2867,19 +2867,19 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C65" t="s">
         <v>16</v>
       </c>
       <c r="D65" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E65" t="s">
         <v>86</v>
       </c>
       <c r="F65" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
@@ -2887,7 +2887,7 @@
         <v>63</v>
       </c>
       <c r="B66" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C66" t="s">
         <v>39</v>
@@ -2896,10 +2896,10 @@
         <v>71</v>
       </c>
       <c r="E66" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F66" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
@@ -2919,7 +2919,7 @@
         <v>65</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
@@ -2927,19 +2927,19 @@
         <v>63</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D68" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E68" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="E68" s="2" t="s">
-        <v>164</v>
-      </c>
       <c r="F68" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
@@ -2959,7 +2959,7 @@
         <v>104</v>
       </c>
       <c r="F69" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
@@ -2967,19 +2967,19 @@
         <v>63</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D70" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E70" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="E70" s="2" t="s">
-        <v>157</v>
-      </c>
       <c r="F70" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
@@ -2999,7 +2999,7 @@
         <v>28</v>
       </c>
       <c r="F71" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
@@ -3007,19 +3007,19 @@
         <v>63</v>
       </c>
       <c r="B72" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C72" t="s">
         <v>23</v>
       </c>
       <c r="D72" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E72" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F72" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
@@ -3027,19 +3027,19 @@
         <v>63</v>
       </c>
       <c r="B73" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D73" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C73" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="D73" s="2" t="s">
+      <c r="E73" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="E73" s="2" t="s">
-        <v>146</v>
-      </c>
       <c r="F73" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
@@ -3047,526 +3047,506 @@
         <v>63</v>
       </c>
       <c r="B74" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C74" t="s">
         <v>7</v>
       </c>
       <c r="D74" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F74" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
-        <v>64</v>
-      </c>
-      <c r="B75" t="s">
-        <v>44</v>
-      </c>
-      <c r="C75" t="s">
-        <v>23</v>
-      </c>
-      <c r="D75" t="s">
-        <v>89</v>
-      </c>
-      <c r="E75" t="s">
-        <v>320</v>
-      </c>
-      <c r="F75" t="s">
-        <v>322</v>
+        <v>63</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B76" t="s">
-        <v>295</v>
+        <v>95</v>
       </c>
       <c r="C76" t="s">
-        <v>303</v>
+        <v>284</v>
       </c>
       <c r="D76" t="s">
-        <v>24</v>
+        <v>89</v>
+      </c>
+      <c r="E76" t="s">
+        <v>96</v>
       </c>
       <c r="F76" t="s">
-        <v>282</v>
+        <v>335</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
-        <v>65</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E77" s="2"/>
-      <c r="F77" s="2" t="s">
-        <v>282</v>
+        <v>64</v>
+      </c>
+      <c r="B77" t="s">
+        <v>44</v>
+      </c>
+      <c r="C77" t="s">
+        <v>23</v>
+      </c>
+      <c r="D77" t="s">
+        <v>89</v>
+      </c>
+      <c r="E77" t="s">
+        <v>319</v>
+      </c>
+      <c r="F77" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B78" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="C78" t="s">
-        <v>16</v>
+        <v>302</v>
       </c>
       <c r="D78" t="s">
         <v>24</v>
       </c>
       <c r="F78" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B80" t="s">
-        <v>153</v>
+        <v>298</v>
       </c>
       <c r="C80" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="D80" t="s">
-        <v>30</v>
-      </c>
-      <c r="E80" t="s">
-        <v>154</v>
+        <v>24</v>
       </c>
       <c r="F80" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>206</v>
+        <v>299</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>14</v>
+        <v>305</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>333</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="E81" s="2"/>
       <c r="F81" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B82" t="s">
-        <v>204</v>
+        <v>152</v>
       </c>
       <c r="C82" t="s">
-        <v>286</v>
+        <v>39</v>
       </c>
       <c r="D82" t="s">
-        <v>316</v>
+        <v>30</v>
       </c>
       <c r="E82" t="s">
-        <v>205</v>
+        <v>153</v>
       </c>
       <c r="F82" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>141</v>
+        <v>205</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D83" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84">
+        <v>72</v>
+      </c>
+      <c r="B84" t="s">
+        <v>203</v>
+      </c>
+      <c r="C84" t="s">
+        <v>285</v>
+      </c>
+      <c r="D84" t="s">
         <v>315</v>
       </c>
-      <c r="E83" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F83" s="2" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="2">
-        <v>75</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="F84" s="2" t="s">
-        <v>282</v>
+      <c r="E84" t="s">
+        <v>204</v>
+      </c>
+      <c r="F84" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>23</v>
+        <v>290</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="E85" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>94</v>
+      </c>
       <c r="F85" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>160</v>
+        <v>105</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>285</v>
+        <v>23</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>161</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="E86" s="2"/>
       <c r="F86" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
+        <v>79</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88" s="2">
         <v>80</v>
       </c>
-      <c r="B87" s="2" t="s">
+      <c r="B88" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C87" s="2" t="s">
+      <c r="C88" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D87" s="2" t="s">
+      <c r="D88" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E87" s="2" t="s">
+      <c r="E88" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F87" s="2" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88">
+      <c r="F88" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89">
         <v>80</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B89" t="s">
         <v>6</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C89" t="s">
         <v>7</v>
       </c>
-      <c r="D88" t="s">
+      <c r="D89" t="s">
         <v>8</v>
       </c>
-      <c r="E88" t="s">
+      <c r="E89" t="s">
         <v>9</v>
       </c>
-      <c r="F88" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="2">
+      <c r="F89" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90" s="2">
         <v>81</v>
       </c>
-      <c r="B89" s="2" t="s">
+      <c r="B90" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C89" s="2" t="s">
+      <c r="C90" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="2" t="s">
+      <c r="D90" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E89" s="2" t="s">
+      <c r="E90" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F89" s="2" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90">
-        <v>82</v>
-      </c>
-      <c r="B90" t="s">
-        <v>297</v>
-      </c>
-      <c r="C90" t="s">
-        <v>305</v>
-      </c>
-      <c r="D90" t="s">
-        <v>178</v>
-      </c>
-      <c r="F90" t="s">
-        <v>282</v>
+      <c r="F90" s="2" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B91" t="s">
-        <v>95</v>
+        <v>296</v>
       </c>
       <c r="C91" t="s">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="D91" t="s">
+        <v>177</v>
+      </c>
+      <c r="F91" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <v>86</v>
+      </c>
+      <c r="B92" t="s">
+        <v>117</v>
+      </c>
+      <c r="C92" t="s">
+        <v>39</v>
+      </c>
+      <c r="D92" t="s">
+        <v>118</v>
+      </c>
+      <c r="E92" t="s">
+        <v>119</v>
+      </c>
+      <c r="F92" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93" s="2">
         <v>89</v>
       </c>
-      <c r="E91" t="s">
-        <v>96</v>
-      </c>
-      <c r="F91" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="2">
-        <v>85</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93">
-        <v>86</v>
-      </c>
-      <c r="B93" t="s">
-        <v>117</v>
-      </c>
-      <c r="C93" t="s">
-        <v>39</v>
-      </c>
-      <c r="D93" t="s">
-        <v>118</v>
-      </c>
-      <c r="E93" t="s">
-        <v>119</v>
-      </c>
-      <c r="F93" t="s">
-        <v>282</v>
+      <c r="B93" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>288</v>
+        <v>23</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="2">
-        <v>91</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D95" s="2" t="s">
+      <c r="A95">
+        <v>92</v>
+      </c>
+      <c r="B95" t="s">
+        <v>32</v>
+      </c>
+      <c r="C95" t="s">
+        <v>33</v>
+      </c>
+      <c r="D95" t="s">
         <v>34</v>
       </c>
-      <c r="E95" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F95" s="2" t="s">
-        <v>282</v>
+      <c r="E95" t="s">
+        <v>35</v>
+      </c>
+      <c r="F95" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C96" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D96" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E96" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F96" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97">
-        <v>94</v>
-      </c>
-      <c r="B97" t="s">
-        <v>38</v>
-      </c>
-      <c r="C97" t="s">
-        <v>39</v>
-      </c>
-      <c r="D97" t="s">
-        <v>40</v>
-      </c>
-      <c r="E97" t="s">
-        <v>41</v>
-      </c>
-      <c r="F97" t="s">
-        <v>282</v>
+      <c r="A97" s="2">
+        <v>95</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="2">
-        <v>95</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F98" s="2" t="s">
-        <v>282</v>
+      <c r="A98">
+        <v>96</v>
+      </c>
+      <c r="B98" t="s">
+        <v>83</v>
+      </c>
+      <c r="C98" t="s">
+        <v>290</v>
+      </c>
+      <c r="D98" t="s">
+        <v>84</v>
+      </c>
+      <c r="E98" t="s">
+        <v>85</v>
+      </c>
+      <c r="F98" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99">
-        <v>96</v>
-      </c>
-      <c r="B99" t="s">
-        <v>83</v>
-      </c>
-      <c r="C99" t="s">
-        <v>291</v>
-      </c>
-      <c r="D99" t="s">
-        <v>84</v>
-      </c>
-      <c r="E99" t="s">
-        <v>85</v>
-      </c>
-      <c r="F99" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="2">
+      <c r="A99" s="2">
         <v>97</v>
       </c>
-      <c r="B100" s="2" t="s">
+      <c r="B99" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D99" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C100" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D100" s="2" t="s">
+      <c r="E99" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="E100" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="F100" s="2" t="s">
-        <v>282</v>
+      <c r="F99" s="2" t="s">
+        <v>281</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F100">
-    <sortCondition ref="A85:A100"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F99">
+    <sortCondition ref="A77:A99"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/kadro/ok.xlsx
+++ b/kadro/ok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kahra\OneDrive\Documents\GitHub\ulkemyanimda.github.io\kadro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D80147D1-5AF4-4D3D-8414-BF6799956367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EF633D4-81D7-4C90-AC1E-34B6677C4ACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="338">
   <si>
     <t>Ad-Soyad</t>
   </si>
@@ -1179,6 +1179,9 @@
   </si>
   <si>
     <t>./img/cayhan.jpg</t>
+  </si>
+  <si>
+    <t>./img/zezberci.jpg</t>
   </si>
 </sst>
 </file>
@@ -3101,131 +3104,131 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
+        <v>63</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78" s="2">
         <v>64</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B78" t="s">
         <v>44</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C78" t="s">
         <v>23</v>
       </c>
-      <c r="D77" t="s">
+      <c r="D78" t="s">
         <v>89</v>
       </c>
-      <c r="E77" t="s">
+      <c r="E78" t="s">
         <v>319</v>
       </c>
-      <c r="F77" t="s">
+      <c r="F78" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79">
         <v>64</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B79" t="s">
         <v>294</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C79" t="s">
         <v>302</v>
       </c>
-      <c r="D78" t="s">
+      <c r="D79" t="s">
         <v>24</v>
       </c>
-      <c r="F78" t="s">
+      <c r="F79" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="2">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A80" s="2">
         <v>65</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="B80" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="C79" s="2" t="s">
+      <c r="C80" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="D79" s="2" t="s">
+      <c r="D80" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E79" s="2"/>
-      <c r="F79" s="2" t="s">
+      <c r="E80" s="2"/>
+      <c r="F80" s="2" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81">
         <v>66</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B81" t="s">
         <v>298</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C81" t="s">
         <v>16</v>
       </c>
-      <c r="D80" t="s">
+      <c r="D81" t="s">
         <v>24</v>
       </c>
-      <c r="F80" t="s">
+      <c r="F81" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="2">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" s="2">
         <v>67</v>
       </c>
-      <c r="B81" s="2" t="s">
+      <c r="B82" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="C82" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="D81" s="2" t="s">
+      <c r="D82" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E81" s="2"/>
-      <c r="F81" s="2" t="s">
+      <c r="E82" s="2"/>
+      <c r="F82" s="2" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83">
         <v>70</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B83" t="s">
         <v>152</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C83" t="s">
         <v>39</v>
       </c>
-      <c r="D82" t="s">
+      <c r="D83" t="s">
         <v>30</v>
       </c>
-      <c r="E82" t="s">
+      <c r="E83" t="s">
         <v>153</v>
       </c>
-      <c r="F82" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="2">
-        <v>71</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="F83" s="2" t="s">
+      <c r="F83" t="s">
         <v>281</v>
       </c>
     </row>
@@ -3546,7 +3549,7 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F99">
-    <sortCondition ref="A77:A99"/>
+    <sortCondition ref="A83:A99"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
